--- a/01_data/01_input_data/02_processed/data_case_russia_LNG_planned.xlsx
+++ b/01_data/01_input_data/02_processed/data_case_russia_LNG_planned.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55CFD503-7E71-4B8B-9BA2-D79A26C9AA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D14237B-8AD8-4905-B141-CA183AE1CB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="103">
   <si>
     <t>Commodities</t>
   </si>
@@ -331,6 +331,24 @@
   </si>
   <si>
     <t>ES_Prod</t>
+  </si>
+  <si>
+    <t>EE_LNG</t>
+  </si>
+  <si>
+    <t>FI_LNG</t>
+  </si>
+  <si>
+    <t>DE_LNG</t>
+  </si>
+  <si>
+    <t>IE_LNG</t>
+  </si>
+  <si>
+    <t>LV_LNG</t>
+  </si>
+  <si>
+    <t>EE</t>
   </si>
 </sst>
 </file>
@@ -688,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0CB446-BDDD-415D-AF22-2CEB1FE45CA5}">
-  <dimension ref="A1:A84"/>
+  <dimension ref="A1:A89"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -823,291 +841,316 @@
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>59</v>
+        <v>96</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1143,7 +1186,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B142"/>
+  <dimension ref="A1:B147"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -1252,23 +1295,23 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="B16" t="s">
         <v>42</v>
@@ -1276,186 +1319,186 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" t="s">
         <v>16</v>
-      </c>
-      <c r="B32" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B34" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" t="s">
         <v>42</v>
-      </c>
-      <c r="B36" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="B37" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" t="s">
         <v>42</v>
-      </c>
-      <c r="B39" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
@@ -1463,7 +1506,7 @@
         <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
@@ -1471,7 +1514,7 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
@@ -1479,7 +1522,7 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
@@ -1487,68 +1530,68 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="B47" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="B48" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="B49" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
+        <v>60</v>
+      </c>
+      <c r="B50" t="s">
         <v>22</v>
-      </c>
-      <c r="B50" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="B51" t="s">
         <v>64</v>
@@ -1556,223 +1599,223 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B52" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="B54" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="B55" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" t="s">
         <v>64</v>
-      </c>
-      <c r="B56" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="B57" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
+        <v>61</v>
+      </c>
+      <c r="B59" t="s">
         <v>18</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="B60" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B62" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B63" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="B64" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="B65" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="B66" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="B67" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="B68" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B69" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B70" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B71" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B72" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B73" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
+        <v>65</v>
+      </c>
+      <c r="B74" t="s">
         <v>66</v>
-      </c>
-      <c r="B74" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B75" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B76" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B77" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B78" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B79" t="s">
         <v>51</v>
@@ -1780,223 +1823,223 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
+        <v>67</v>
+      </c>
+      <c r="B80" t="s">
         <v>68</v>
-      </c>
-      <c r="B80" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B81" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="B82" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="B83" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
+        <v>68</v>
+      </c>
+      <c r="B84" t="s">
         <v>51</v>
-      </c>
-      <c r="B84" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="B85" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="B86" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B87" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="B88" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="B89" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="B90" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="B91" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B92" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B93" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="B94" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="B95" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="B96" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="B97" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="B98" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B99" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B100" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B101" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="B102" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="B103" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B104" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="B105" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B106" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="B107" t="s">
         <v>22</v>
@@ -2004,281 +2047,321 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="B108" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="B110" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="B111" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B112" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B113" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="B114" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B115" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="B116" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B117" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="B118" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B119" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B120" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="B121" t="s">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="B122" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B123" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B124" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="B125" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="B126" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B127" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="B128" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="B129" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B130" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="B131" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B132" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B133" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B134" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B135" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B137" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B138" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B139" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B140" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B141" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
+        <v>91</v>
+      </c>
+      <c r="B142" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>92</v>
+      </c>
+      <c r="B143" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>93</v>
+      </c>
+      <c r="B144" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>94</v>
+      </c>
+      <c r="B145" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>95</v>
+      </c>
+      <c r="B146" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
         <v>96</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B147" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2289,7 +2372,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I285"/>
+  <dimension ref="A1:I295"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -2674,16 +2757,16 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="D14">
-        <v>10000</v>
+        <v>24.424999999999997</v>
       </c>
       <c r="E14">
-        <v>10000</v>
+        <v>24.424999999999997</v>
       </c>
       <c r="F14">
         <v>100</v>
@@ -2703,16 +2786,16 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D15">
-        <v>10000</v>
+        <v>48.849999999999994</v>
       </c>
       <c r="E15">
-        <v>10000</v>
+        <v>48.849999999999994</v>
       </c>
       <c r="F15">
         <v>100</v>
@@ -2732,16 +2815,16 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D16">
-        <v>10000</v>
+        <v>304.82399999999996</v>
       </c>
       <c r="E16">
-        <v>10000</v>
+        <v>304.82399999999996</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -2761,16 +2844,16 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D17">
-        <v>10000</v>
+        <v>25.402000000000001</v>
       </c>
       <c r="E17">
-        <v>10000</v>
+        <v>25.402000000000001</v>
       </c>
       <c r="F17">
         <v>100</v>
@@ -2790,16 +2873,16 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D18">
-        <v>10000</v>
+        <v>14.654999999999999</v>
       </c>
       <c r="E18">
-        <v>10000</v>
+        <v>14.654999999999999</v>
       </c>
       <c r="F18">
         <v>100</v>
@@ -2819,10 +2902,10 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="D19">
         <v>10000</v>
@@ -2848,10 +2931,10 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="D20">
         <v>10000</v>
@@ -2877,10 +2960,10 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="D21">
         <v>10000</v>
@@ -2906,10 +2989,10 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D22">
         <v>10000</v>
@@ -2935,10 +3018,10 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D23">
         <v>10000</v>
@@ -2964,10 +3047,10 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="D24">
         <v>10000</v>
@@ -2993,10 +3076,10 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D25">
         <v>10000</v>
@@ -3022,10 +3105,10 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="D26">
         <v>10000</v>
@@ -3051,10 +3134,10 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="D27">
         <v>10000</v>
@@ -3080,10 +3163,10 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="D28">
         <v>10000</v>
@@ -3109,10 +3192,10 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="D29">
         <v>10000</v>
@@ -3138,10 +3221,10 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D30">
         <v>10000</v>
@@ -3150,7 +3233,7 @@
         <v>10000</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G30">
         <v>10000000</v>
@@ -3167,10 +3250,10 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D31">
         <v>10000</v>
@@ -3179,7 +3262,7 @@
         <v>10000</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G31">
         <v>10000000</v>
@@ -3196,10 +3279,10 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D32">
         <v>10000</v>
@@ -3208,7 +3291,7 @@
         <v>10000</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G32">
         <v>10000000</v>
@@ -3225,10 +3308,10 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D33">
         <v>10000</v>
@@ -3237,7 +3320,7 @@
         <v>10000</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G33">
         <v>10000000</v>
@@ -3254,10 +3337,10 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D34">
         <v>10000</v>
@@ -3266,7 +3349,7 @@
         <v>10000</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G34">
         <v>10000000</v>
@@ -3283,10 +3366,10 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="D35">
         <v>10000</v>
@@ -3312,10 +3395,10 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C36" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D36">
         <v>10000</v>
@@ -3341,10 +3424,10 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D37">
         <v>10000</v>
@@ -3370,10 +3453,10 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C38" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="D38">
         <v>10000</v>
@@ -3399,10 +3482,10 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C39" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D39">
         <v>10000</v>
@@ -3411,7 +3494,7 @@
         <v>10000</v>
       </c>
       <c r="F39">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="G39">
         <v>10000000</v>
@@ -3428,10 +3511,10 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="D40">
         <v>10000</v>
@@ -3457,10 +3540,10 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C41" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D41">
         <v>10000</v>
@@ -3486,10 +3569,10 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="D42">
         <v>10000</v>
@@ -3515,16 +3598,16 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="D43">
-        <v>237.87050000000002</v>
+        <v>10000</v>
       </c>
       <c r="E43">
-        <v>237.87050000000002</v>
+        <v>10000</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -3544,19 +3627,19 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C44" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D44">
-        <v>140.52500000000001</v>
+        <v>10000</v>
       </c>
       <c r="E44">
-        <v>140.52500000000001</v>
+        <v>10000</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="G44">
         <v>10000000</v>
@@ -3573,16 +3656,16 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C45" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D45">
-        <v>293.24099999999999</v>
+        <v>10000</v>
       </c>
       <c r="E45">
-        <v>293.24099999999999</v>
+        <v>10000</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -3602,16 +3685,16 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D46">
-        <v>120.88800000000001</v>
+        <v>10000</v>
       </c>
       <c r="E46">
-        <v>120.88800000000001</v>
+        <v>10000</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -3631,16 +3714,16 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C47" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D47">
-        <v>117.81104999999999</v>
+        <v>10000</v>
       </c>
       <c r="E47">
-        <v>117.81104999999999</v>
+        <v>10000</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -3660,16 +3743,16 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" t="s">
         <v>16</v>
       </c>
-      <c r="C48" t="s">
-        <v>18</v>
-      </c>
       <c r="D48">
-        <v>317.55</v>
+        <v>237.87050000000002</v>
       </c>
       <c r="E48">
-        <v>317.55</v>
+        <v>237.87050000000002</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -3689,16 +3772,16 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D49">
-        <v>509.97800000000001</v>
+        <v>140.52500000000001</v>
       </c>
       <c r="E49">
-        <v>509.97800000000001</v>
+        <v>140.52500000000001</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -3718,16 +3801,16 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D50">
-        <v>702.90714500000001</v>
+        <v>293.24099999999999</v>
       </c>
       <c r="E50">
-        <v>702.90714500000001</v>
+        <v>293.24099999999999</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -3747,16 +3830,16 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D51">
-        <v>144.59475</v>
+        <v>120.88800000000001</v>
       </c>
       <c r="E51">
-        <v>144.59475</v>
+        <v>120.88800000000001</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -3776,16 +3859,16 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="s">
         <v>42</v>
       </c>
-      <c r="C52" t="s">
-        <v>28</v>
-      </c>
       <c r="D52">
-        <v>594.33059500000013</v>
+        <v>117.81104999999999</v>
       </c>
       <c r="E52">
-        <v>594.33059500000013</v>
+        <v>117.81104999999999</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -3805,16 +3888,16 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="D53">
-        <v>125.65051999999997</v>
+        <v>317.55</v>
       </c>
       <c r="E53">
-        <v>125.65051999999997</v>
+        <v>317.55</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -3834,16 +3917,16 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="D54">
-        <v>119.72</v>
+        <v>509.97800000000001</v>
       </c>
       <c r="E54">
-        <v>119.72</v>
+        <v>509.97800000000001</v>
       </c>
       <c r="F54">
         <v>1</v>
@@ -3863,16 +3946,16 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
+        <v>28</v>
+      </c>
+      <c r="C55" t="s">
         <v>42</v>
       </c>
-      <c r="C55" t="s">
-        <v>18</v>
-      </c>
       <c r="D55">
-        <v>224.00633999999999</v>
+        <v>702.90714500000001</v>
       </c>
       <c r="E55">
-        <v>224.00633999999999</v>
+        <v>702.90714500000001</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -3895,13 +3978,13 @@
         <v>42</v>
       </c>
       <c r="C56" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D56">
-        <v>49.680879999999995</v>
+        <v>144.59475</v>
       </c>
       <c r="E56">
-        <v>49.680879999999995</v>
+        <v>144.59475</v>
       </c>
       <c r="F56">
         <v>1</v>
@@ -3924,13 +4007,13 @@
         <v>42</v>
       </c>
       <c r="C57" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D57">
-        <v>85.227500000000006</v>
+        <v>594.33059500000013</v>
       </c>
       <c r="E57">
-        <v>85.227500000000006</v>
+        <v>594.33059500000013</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -3953,13 +4036,13 @@
         <v>42</v>
       </c>
       <c r="C58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D58">
-        <v>658.37605000000008</v>
+        <v>125.65051999999997</v>
       </c>
       <c r="E58">
-        <v>658.37605000000008</v>
+        <v>125.65051999999997</v>
       </c>
       <c r="F58">
         <v>1</v>
@@ -3982,13 +4065,13 @@
         <v>42</v>
       </c>
       <c r="C59" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D59">
-        <v>9.7491500000000002</v>
+        <v>119.72</v>
       </c>
       <c r="E59">
-        <v>9.7491500000000002</v>
+        <v>119.72</v>
       </c>
       <c r="F59">
         <v>1</v>
@@ -4008,16 +4091,16 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C60" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D60">
-        <v>124.08832</v>
+        <v>224.00633999999999</v>
       </c>
       <c r="E60">
-        <v>124.08832</v>
+        <v>224.00633999999999</v>
       </c>
       <c r="F60">
         <v>1</v>
@@ -4037,16 +4120,16 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C61" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D61">
-        <v>419.75</v>
+        <v>49.680879999999995</v>
       </c>
       <c r="E61">
-        <v>419.75</v>
+        <v>49.680879999999995</v>
       </c>
       <c r="F61">
         <v>1</v>
@@ -4066,16 +4149,16 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C62" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="D62">
-        <v>41.0625</v>
+        <v>85.227500000000006</v>
       </c>
       <c r="E62">
-        <v>41.0625</v>
+        <v>85.227500000000006</v>
       </c>
       <c r="F62">
         <v>1</v>
@@ -4095,16 +4178,16 @@
         <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C63" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D63">
-        <v>89.972499999999997</v>
+        <v>658.37605000000008</v>
       </c>
       <c r="E63">
-        <v>89.972499999999997</v>
+        <v>658.37605000000008</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -4124,16 +4207,16 @@
         <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C64" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D64">
-        <v>55.881500000000003</v>
+        <v>9.7491500000000002</v>
       </c>
       <c r="E64">
-        <v>55.881500000000003</v>
+        <v>9.7491500000000002</v>
       </c>
       <c r="F64">
         <v>1</v>
@@ -4153,16 +4236,16 @@
         <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C65" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D65">
-        <v>70.627499999999998</v>
+        <v>124.08832</v>
       </c>
       <c r="E65">
-        <v>70.627499999999998</v>
+        <v>124.08832</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -4182,16 +4265,16 @@
         <v>11</v>
       </c>
       <c r="B66" t="s">
+        <v>60</v>
+      </c>
+      <c r="C66" t="s">
         <v>22</v>
       </c>
-      <c r="C66" t="s">
-        <v>61</v>
-      </c>
       <c r="D66">
-        <v>157.46100000000001</v>
+        <v>419.75</v>
       </c>
       <c r="E66">
-        <v>157.46100000000001</v>
+        <v>419.75</v>
       </c>
       <c r="F66">
         <v>1</v>
@@ -4211,16 +4294,16 @@
         <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C67" t="s">
         <v>64</v>
       </c>
       <c r="D67">
-        <v>10.4025</v>
+        <v>41.0625</v>
       </c>
       <c r="E67">
-        <v>10.4025</v>
+        <v>41.0625</v>
       </c>
       <c r="F67">
         <v>1</v>
@@ -4240,16 +4323,16 @@
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C68" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D68">
-        <v>63.07200000000001</v>
+        <v>89.972499999999997</v>
       </c>
       <c r="E68">
-        <v>63.07200000000001</v>
+        <v>89.972499999999997</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -4269,16 +4352,16 @@
         <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C69" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="D69">
-        <v>233.74600000000001</v>
+        <v>55.881500000000003</v>
       </c>
       <c r="E69">
-        <v>233.74600000000001</v>
+        <v>55.881500000000003</v>
       </c>
       <c r="F69">
         <v>1</v>
@@ -4298,16 +4381,16 @@
         <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C70" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="D70">
-        <v>36.5</v>
+        <v>70.627499999999998</v>
       </c>
       <c r="E70">
-        <v>36.5</v>
+        <v>70.627499999999998</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -4327,16 +4410,16 @@
         <v>11</v>
       </c>
       <c r="B71" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="C71" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="D71">
-        <v>7.8475000000000001</v>
+        <v>157.46100000000001</v>
       </c>
       <c r="E71">
-        <v>7.8475000000000001</v>
+        <v>157.46100000000001</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -4356,16 +4439,16 @@
         <v>11</v>
       </c>
       <c r="B72" t="s">
+        <v>22</v>
+      </c>
+      <c r="C72" t="s">
         <v>64</v>
       </c>
-      <c r="C72" t="s">
-        <v>24</v>
-      </c>
       <c r="D72">
-        <v>19.6005</v>
+        <v>10.4025</v>
       </c>
       <c r="E72">
-        <v>19.6005</v>
+        <v>10.4025</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -4385,16 +4468,16 @@
         <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C73" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D73">
-        <v>2.8105000000000002</v>
+        <v>63.07200000000001</v>
       </c>
       <c r="E73">
-        <v>2.8105000000000002</v>
+        <v>63.07200000000001</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -4414,16 +4497,16 @@
         <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C74" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D74">
-        <v>17.72805</v>
+        <v>233.74600000000001</v>
       </c>
       <c r="E74">
-        <v>17.72805</v>
+        <v>233.74600000000001</v>
       </c>
       <c r="F74">
         <v>1</v>
@@ -4443,16 +4526,16 @@
         <v>11</v>
       </c>
       <c r="B75" t="s">
+        <v>61</v>
+      </c>
+      <c r="C75" t="s">
         <v>18</v>
       </c>
-      <c r="C75" t="s">
-        <v>16</v>
-      </c>
       <c r="D75">
-        <v>98.55</v>
+        <v>36.5</v>
       </c>
       <c r="E75">
-        <v>98.55</v>
+        <v>36.5</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -4472,16 +4555,16 @@
         <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="C76" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="D76">
-        <v>81.394999999999996</v>
+        <v>7.8475000000000001</v>
       </c>
       <c r="E76">
-        <v>81.394999999999996</v>
+        <v>7.8475000000000001</v>
       </c>
       <c r="F76">
         <v>1</v>
@@ -4501,16 +4584,16 @@
         <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="C77" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D77">
-        <v>60.068779999999997</v>
+        <v>19.6005</v>
       </c>
       <c r="E77">
-        <v>60.068779999999997</v>
+        <v>19.6005</v>
       </c>
       <c r="F77">
         <v>1</v>
@@ -4530,16 +4613,16 @@
         <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C78" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D78">
-        <v>1.5034349999999999</v>
+        <v>2.8105000000000002</v>
       </c>
       <c r="E78">
-        <v>1.5034349999999999</v>
+        <v>2.8105000000000002</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -4559,16 +4642,16 @@
         <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C79" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D79">
-        <v>340.03399999999999</v>
+        <v>17.72805</v>
       </c>
       <c r="E79">
-        <v>340.03399999999999</v>
+        <v>17.72805</v>
       </c>
       <c r="F79">
         <v>1</v>
@@ -4588,16 +4671,16 @@
         <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="C80" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D80">
-        <v>449.59203500000001</v>
+        <v>98.55</v>
       </c>
       <c r="E80">
-        <v>449.59203500000001</v>
+        <v>98.55</v>
       </c>
       <c r="F80">
         <v>1</v>
@@ -4617,16 +4700,16 @@
         <v>11</v>
       </c>
       <c r="B81" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="C81" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="D81">
-        <v>10.220000000000001</v>
+        <v>81.394999999999996</v>
       </c>
       <c r="E81">
-        <v>10.220000000000001</v>
+        <v>81.394999999999996</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -4646,16 +4729,16 @@
         <v>11</v>
       </c>
       <c r="B82" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="C82" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D82">
-        <v>454.93600000000004</v>
+        <v>60.068779999999997</v>
       </c>
       <c r="E82">
-        <v>454.93600000000004</v>
+        <v>60.068779999999997</v>
       </c>
       <c r="F82">
         <v>1</v>
@@ -4675,16 +4758,16 @@
         <v>11</v>
       </c>
       <c r="B83" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="C83" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D83">
-        <v>573.19600000000003</v>
+        <v>1.5034349999999999</v>
       </c>
       <c r="E83">
-        <v>573.19600000000003</v>
+        <v>1.5034349999999999</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -4704,16 +4787,16 @@
         <v>11</v>
       </c>
       <c r="B84" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="C84" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D84">
-        <v>167.024</v>
+        <v>340.03399999999999</v>
       </c>
       <c r="E84">
-        <v>167.024</v>
+        <v>340.03399999999999</v>
       </c>
       <c r="F84">
         <v>1</v>
@@ -4733,16 +4816,16 @@
         <v>11</v>
       </c>
       <c r="B85" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C85" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D85">
-        <v>47.048499999999997</v>
+        <v>449.59203500000001</v>
       </c>
       <c r="E85">
-        <v>47.048499999999997</v>
+        <v>449.59203500000001</v>
       </c>
       <c r="F85">
         <v>1</v>
@@ -4762,16 +4845,16 @@
         <v>11</v>
       </c>
       <c r="B86" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C86" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="D86">
-        <v>151.84</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="E86">
-        <v>151.84</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="F86">
         <v>1</v>
@@ -4791,16 +4874,16 @@
         <v>11</v>
       </c>
       <c r="B87" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C87" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="D87">
-        <v>28.251000000000005</v>
+        <v>454.93600000000004</v>
       </c>
       <c r="E87">
-        <v>28.251000000000005</v>
+        <v>454.93600000000004</v>
       </c>
       <c r="F87">
         <v>1</v>
@@ -4820,16 +4903,16 @@
         <v>11</v>
       </c>
       <c r="B88" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C88" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D88">
-        <v>18.572295</v>
+        <v>573.19600000000003</v>
       </c>
       <c r="E88">
-        <v>18.572295</v>
+        <v>573.19600000000003</v>
       </c>
       <c r="F88">
         <v>1</v>
@@ -4849,16 +4932,16 @@
         <v>11</v>
       </c>
       <c r="B89" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C89" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D89">
-        <v>51.83</v>
+        <v>167.024</v>
       </c>
       <c r="E89">
-        <v>51.83</v>
+        <v>167.024</v>
       </c>
       <c r="F89">
         <v>1</v>
@@ -4878,16 +4961,16 @@
         <v>11</v>
       </c>
       <c r="B90" t="s">
+        <v>65</v>
+      </c>
+      <c r="C90" t="s">
         <v>66</v>
       </c>
-      <c r="C90" t="s">
-        <v>51</v>
-      </c>
       <c r="D90">
-        <v>28.287500000000001</v>
+        <v>47.048499999999997</v>
       </c>
       <c r="E90">
-        <v>28.287500000000001</v>
+        <v>47.048499999999997</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -4907,16 +4990,16 @@
         <v>11</v>
       </c>
       <c r="B91" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C91" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D91">
-        <v>122.3699</v>
+        <v>151.84</v>
       </c>
       <c r="E91">
-        <v>122.3699</v>
+        <v>151.84</v>
       </c>
       <c r="F91">
         <v>1</v>
@@ -4936,16 +5019,16 @@
         <v>11</v>
       </c>
       <c r="B92" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C92" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="D92">
-        <v>6.5626999999999995</v>
+        <v>28.251000000000005</v>
       </c>
       <c r="E92">
-        <v>6.5626999999999995</v>
+        <v>28.251000000000005</v>
       </c>
       <c r="F92">
         <v>1</v>
@@ -4965,16 +5048,16 @@
         <v>11</v>
       </c>
       <c r="B93" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C93" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D93">
-        <v>170.63749999999999</v>
+        <v>18.572295</v>
       </c>
       <c r="E93">
-        <v>170.63749999999999</v>
+        <v>18.572295</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -4994,16 +5077,16 @@
         <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C94" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="D94">
-        <v>42.997</v>
+        <v>51.83</v>
       </c>
       <c r="E94">
-        <v>42.997</v>
+        <v>51.83</v>
       </c>
       <c r="F94">
         <v>1</v>
@@ -5023,16 +5106,16 @@
         <v>11</v>
       </c>
       <c r="B95" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C95" t="s">
         <v>51</v>
       </c>
       <c r="D95">
-        <v>54.074750000000002</v>
+        <v>28.287500000000001</v>
       </c>
       <c r="E95">
-        <v>54.074750000000002</v>
+        <v>28.287500000000001</v>
       </c>
       <c r="F95">
         <v>1</v>
@@ -5052,16 +5135,16 @@
         <v>11</v>
       </c>
       <c r="B96" t="s">
+        <v>67</v>
+      </c>
+      <c r="C96" t="s">
         <v>68</v>
       </c>
-      <c r="C96" t="s">
-        <v>36</v>
-      </c>
       <c r="D96">
-        <v>181.46340000000004</v>
+        <v>122.3699</v>
       </c>
       <c r="E96">
-        <v>181.46340000000004</v>
+        <v>122.3699</v>
       </c>
       <c r="F96">
         <v>1</v>
@@ -5081,16 +5164,16 @@
         <v>11</v>
       </c>
       <c r="B97" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C97" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D97">
-        <v>23.659299999999998</v>
+        <v>6.5626999999999995</v>
       </c>
       <c r="E97">
-        <v>23.659299999999998</v>
+        <v>6.5626999999999995</v>
       </c>
       <c r="F97">
         <v>1</v>
@@ -5110,16 +5193,16 @@
         <v>11</v>
       </c>
       <c r="B98" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C98" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D98">
-        <v>18.359500000000001</v>
+        <v>170.63749999999999</v>
       </c>
       <c r="E98">
-        <v>18.359500000000001</v>
+        <v>170.63749999999999</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -5139,16 +5222,16 @@
         <v>11</v>
       </c>
       <c r="B99" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C99" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="D99">
-        <v>294.09875000000005</v>
+        <v>42.997</v>
       </c>
       <c r="E99">
-        <v>294.09875000000005</v>
+        <v>42.997</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -5168,16 +5251,16 @@
         <v>11</v>
       </c>
       <c r="B100" t="s">
+        <v>68</v>
+      </c>
+      <c r="C100" t="s">
         <v>51</v>
       </c>
-      <c r="C100" t="s">
-        <v>58</v>
-      </c>
       <c r="D100">
-        <v>44.603000000000002</v>
+        <v>54.074750000000002</v>
       </c>
       <c r="E100">
-        <v>44.603000000000002</v>
+        <v>54.074750000000002</v>
       </c>
       <c r="F100">
         <v>1</v>
@@ -5197,16 +5280,16 @@
         <v>11</v>
       </c>
       <c r="B101" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C101" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="D101">
-        <v>20.330500000000001</v>
+        <v>181.46340000000004</v>
       </c>
       <c r="E101">
-        <v>20.330500000000001</v>
+        <v>181.46340000000004</v>
       </c>
       <c r="F101">
         <v>1</v>
@@ -5226,16 +5309,16 @@
         <v>11</v>
       </c>
       <c r="B102" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C102" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D102">
-        <v>24.673999999999996</v>
+        <v>23.659299999999998</v>
       </c>
       <c r="E102">
-        <v>24.673999999999996</v>
+        <v>23.659299999999998</v>
       </c>
       <c r="F102">
         <v>1</v>
@@ -5255,16 +5338,16 @@
         <v>11</v>
       </c>
       <c r="B103" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C103" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D103">
-        <v>41.683</v>
+        <v>18.359500000000001</v>
       </c>
       <c r="E103">
-        <v>41.683</v>
+        <v>18.359500000000001</v>
       </c>
       <c r="F103">
         <v>1</v>
@@ -5284,16 +5367,16 @@
         <v>11</v>
       </c>
       <c r="B104" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C104" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="D104">
-        <v>23.761499999999998</v>
+        <v>294.09875000000005</v>
       </c>
       <c r="E104">
-        <v>23.761499999999998</v>
+        <v>294.09875000000005</v>
       </c>
       <c r="F104">
         <v>1</v>
@@ -5313,16 +5396,16 @@
         <v>11</v>
       </c>
       <c r="B105" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C105" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D105">
-        <v>31.024999999999999</v>
+        <v>44.603000000000002</v>
       </c>
       <c r="E105">
-        <v>31.024999999999999</v>
+        <v>44.603000000000002</v>
       </c>
       <c r="F105">
         <v>1</v>
@@ -5342,16 +5425,16 @@
         <v>11</v>
       </c>
       <c r="B106" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C106" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="D106">
-        <v>81.906000000000006</v>
+        <v>20.330500000000001</v>
       </c>
       <c r="E106">
-        <v>81.906000000000006</v>
+        <v>20.330500000000001</v>
       </c>
       <c r="F106">
         <v>1</v>
@@ -5371,16 +5454,16 @@
         <v>11</v>
       </c>
       <c r="B107" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C107" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="D107">
-        <v>52.56</v>
+        <v>24.673999999999996</v>
       </c>
       <c r="E107">
-        <v>52.56</v>
+        <v>24.673999999999996</v>
       </c>
       <c r="F107">
         <v>1</v>
@@ -5400,19 +5483,19 @@
         <v>11</v>
       </c>
       <c r="B108" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C108" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D108">
-        <v>29.2</v>
+        <v>41.683</v>
       </c>
       <c r="E108">
-        <v>29.2</v>
+        <v>41.683</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="G108">
         <v>10000000</v>
@@ -5429,16 +5512,16 @@
         <v>11</v>
       </c>
       <c r="B109" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C109" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D109">
-        <v>49.494</v>
+        <v>23.761499999999998</v>
       </c>
       <c r="E109">
-        <v>49.494</v>
+        <v>23.761499999999998</v>
       </c>
       <c r="F109">
         <v>1</v>
@@ -5458,19 +5541,19 @@
         <v>11</v>
       </c>
       <c r="B110" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C110" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D110">
-        <v>816.06700000000012</v>
+        <v>31.024999999999999</v>
       </c>
       <c r="E110">
-        <v>816.06700000000012</v>
+        <v>31.024999999999999</v>
       </c>
       <c r="F110">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="G110">
         <v>10000000</v>
@@ -5487,16 +5570,16 @@
         <v>11</v>
       </c>
       <c r="B111" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C111" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="D111">
-        <v>188.88749999999999</v>
+        <v>81.906000000000006</v>
       </c>
       <c r="E111">
-        <v>188.88749999999999</v>
+        <v>81.906000000000006</v>
       </c>
       <c r="F111">
         <v>1</v>
@@ -5516,16 +5599,16 @@
         <v>11</v>
       </c>
       <c r="B112" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C112" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D112">
-        <v>424.64100000000008</v>
+        <v>52.56</v>
       </c>
       <c r="E112">
-        <v>424.64100000000008</v>
+        <v>52.56</v>
       </c>
       <c r="F112">
         <v>1</v>
@@ -5545,16 +5628,16 @@
         <v>11</v>
       </c>
       <c r="B113" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="C113" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="D113">
-        <v>0.80300000000000016</v>
+        <v>29.2</v>
       </c>
       <c r="E113">
-        <v>0.80300000000000016</v>
+        <v>29.2</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -5574,16 +5657,16 @@
         <v>11</v>
       </c>
       <c r="B114" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C114" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D114">
-        <v>635.83000000000004</v>
+        <v>49.494</v>
       </c>
       <c r="E114">
-        <v>635.83000000000004</v>
+        <v>49.494</v>
       </c>
       <c r="F114">
         <v>1</v>
@@ -5603,16 +5686,16 @@
         <v>11</v>
       </c>
       <c r="B115" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C115" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D115">
-        <v>61.32</v>
+        <v>816.06700000000012</v>
       </c>
       <c r="E115">
-        <v>61.32</v>
+        <v>816.06700000000012</v>
       </c>
       <c r="F115">
         <v>1</v>
@@ -5632,16 +5715,16 @@
         <v>11</v>
       </c>
       <c r="B116" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C116" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D116">
-        <v>80.3</v>
+        <v>188.88749999999999</v>
       </c>
       <c r="E116">
-        <v>80.3</v>
+        <v>188.88749999999999</v>
       </c>
       <c r="F116">
         <v>1</v>
@@ -5661,16 +5744,16 @@
         <v>11</v>
       </c>
       <c r="B117" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C117" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="D117">
-        <v>200.71350000000001</v>
+        <v>424.64100000000008</v>
       </c>
       <c r="E117">
-        <v>200.71350000000001</v>
+        <v>424.64100000000008</v>
       </c>
       <c r="F117">
         <v>1</v>
@@ -5690,16 +5773,16 @@
         <v>11</v>
       </c>
       <c r="B118" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="C118" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D118">
-        <v>256.15699999999998</v>
+        <v>0.80300000000000016</v>
       </c>
       <c r="E118">
-        <v>256.15699999999998</v>
+        <v>0.80300000000000016</v>
       </c>
       <c r="F118">
         <v>1</v>
@@ -5719,16 +5802,16 @@
         <v>11</v>
       </c>
       <c r="B119" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C119" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="D119">
-        <v>145.489</v>
+        <v>635.83000000000004</v>
       </c>
       <c r="E119">
-        <v>145.489</v>
+        <v>635.83000000000004</v>
       </c>
       <c r="F119">
         <v>1</v>
@@ -5748,16 +5831,16 @@
         <v>11</v>
       </c>
       <c r="B120" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C120" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="D120">
-        <v>161.62200000000001</v>
+        <v>61.32</v>
       </c>
       <c r="E120">
-        <v>161.62200000000001</v>
+        <v>61.32</v>
       </c>
       <c r="F120">
         <v>1</v>
@@ -5777,16 +5860,16 @@
         <v>11</v>
       </c>
       <c r="B121" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="C121" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="D121">
-        <v>439.27749999999992</v>
+        <v>80.3</v>
       </c>
       <c r="E121">
-        <v>439.27749999999992</v>
+        <v>80.3</v>
       </c>
       <c r="F121">
         <v>1</v>
@@ -5806,16 +5889,16 @@
         <v>11</v>
       </c>
       <c r="B122" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="C122" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="D122">
-        <v>439.27749999999992</v>
+        <v>200.71350000000001</v>
       </c>
       <c r="E122">
-        <v>439.27749999999992</v>
+        <v>200.71350000000001</v>
       </c>
       <c r="F122">
         <v>1</v>
@@ -5835,16 +5918,16 @@
         <v>11</v>
       </c>
       <c r="B123" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="C123" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="D123">
-        <v>118.77099999999999</v>
+        <v>256.15699999999998</v>
       </c>
       <c r="E123">
-        <v>118.77099999999999</v>
+        <v>256.15699999999998</v>
       </c>
       <c r="F123">
         <v>1</v>
@@ -5864,16 +5947,16 @@
         <v>11</v>
       </c>
       <c r="B124" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C124" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="D124">
-        <v>486.91</v>
+        <v>145.489</v>
       </c>
       <c r="E124">
-        <v>486.91</v>
+        <v>145.489</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -5893,16 +5976,16 @@
         <v>11</v>
       </c>
       <c r="B125" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C125" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D125">
-        <v>144.17500000000001</v>
+        <v>161.62200000000001</v>
       </c>
       <c r="E125">
-        <v>144.17500000000001</v>
+        <v>161.62200000000001</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -5922,16 +6005,16 @@
         <v>11</v>
       </c>
       <c r="B126" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C126" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="D126">
-        <v>89.716999999999999</v>
+        <v>439.27749999999992</v>
       </c>
       <c r="E126">
-        <v>89.716999999999999</v>
+        <v>439.27749999999992</v>
       </c>
       <c r="F126">
         <v>1</v>
@@ -5951,16 +6034,16 @@
         <v>11</v>
       </c>
       <c r="B127" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C127" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D127">
-        <v>12.1837</v>
+        <v>439.27749999999992</v>
       </c>
       <c r="E127">
-        <v>12.1837</v>
+        <v>439.27749999999992</v>
       </c>
       <c r="F127">
         <v>1</v>
@@ -5980,16 +6063,16 @@
         <v>11</v>
       </c>
       <c r="B128" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C128" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D128">
-        <v>180.20050000000001</v>
+        <v>118.77099999999999</v>
       </c>
       <c r="E128">
-        <v>180.20050000000001</v>
+        <v>118.77099999999999</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -6009,16 +6092,16 @@
         <v>11</v>
       </c>
       <c r="B129" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C129" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="D129">
-        <v>421.21</v>
+        <v>486.91</v>
       </c>
       <c r="E129">
-        <v>421.21</v>
+        <v>486.91</v>
       </c>
       <c r="F129">
         <v>1</v>
@@ -6038,16 +6121,16 @@
         <v>11</v>
       </c>
       <c r="B130" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C130" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D130">
-        <v>123.04150000000001</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="E130">
-        <v>123.04150000000001</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="F130">
         <v>1</v>
@@ -6067,16 +6150,16 @@
         <v>11</v>
       </c>
       <c r="B131" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="C131" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D131">
-        <v>455.15499999999997</v>
+        <v>89.716999999999999</v>
       </c>
       <c r="E131">
-        <v>455.15499999999997</v>
+        <v>89.716999999999999</v>
       </c>
       <c r="F131">
         <v>1</v>
@@ -6096,16 +6179,16 @@
         <v>11</v>
       </c>
       <c r="B132" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="C132" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="D132">
-        <v>351.714</v>
+        <v>12.1837</v>
       </c>
       <c r="E132">
-        <v>351.714</v>
+        <v>12.1837</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -6125,16 +6208,16 @@
         <v>11</v>
       </c>
       <c r="B133" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C133" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D133">
-        <v>167.75399999999999</v>
+        <v>180.20050000000001</v>
       </c>
       <c r="E133">
-        <v>167.75399999999999</v>
+        <v>180.20050000000001</v>
       </c>
       <c r="F133">
         <v>1</v>
@@ -6154,16 +6237,16 @@
         <v>11</v>
       </c>
       <c r="B134" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C134" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D134">
-        <v>207.5025</v>
+        <v>421.21</v>
       </c>
       <c r="E134">
-        <v>207.5025</v>
+        <v>421.21</v>
       </c>
       <c r="F134">
         <v>1</v>
@@ -6183,16 +6266,16 @@
         <v>11</v>
       </c>
       <c r="B135" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="C135" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D135">
-        <v>513.19000000000005</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="E135">
-        <v>513.19000000000005</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="F135">
         <v>1</v>
@@ -6212,16 +6295,16 @@
         <v>11</v>
       </c>
       <c r="B136" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C136" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D136">
-        <v>67.451999999999998</v>
+        <v>455.15499999999997</v>
       </c>
       <c r="E136">
-        <v>67.451999999999998</v>
+        <v>455.15499999999997</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -6241,16 +6324,16 @@
         <v>11</v>
       </c>
       <c r="B137" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C137" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="D137">
-        <v>200.71350000000001</v>
+        <v>351.714</v>
       </c>
       <c r="E137">
-        <v>200.71350000000001</v>
+        <v>351.714</v>
       </c>
       <c r="F137">
         <v>1</v>
@@ -6270,16 +6353,16 @@
         <v>11</v>
       </c>
       <c r="B138" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C138" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D138">
-        <v>144.17500000000001</v>
+        <v>167.75399999999999</v>
       </c>
       <c r="E138">
-        <v>144.17500000000001</v>
+        <v>167.75399999999999</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -6299,16 +6382,16 @@
         <v>11</v>
       </c>
       <c r="B139" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="C139" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="D139">
-        <v>123.04150000000001</v>
+        <v>207.5025</v>
       </c>
       <c r="E139">
-        <v>123.04150000000001</v>
+        <v>207.5025</v>
       </c>
       <c r="F139">
         <v>1</v>
@@ -6328,16 +6411,16 @@
         <v>11</v>
       </c>
       <c r="B140" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="C140" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D140">
-        <v>421.21</v>
+        <v>513.19000000000005</v>
       </c>
       <c r="E140">
-        <v>421.21</v>
+        <v>513.19000000000005</v>
       </c>
       <c r="F140">
         <v>1</v>
@@ -6357,16 +6440,16 @@
         <v>11</v>
       </c>
       <c r="B141" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C141" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="D141">
-        <v>14.965</v>
+        <v>67.451999999999998</v>
       </c>
       <c r="E141">
-        <v>14.965</v>
+        <v>67.451999999999998</v>
       </c>
       <c r="F141">
         <v>1</v>
@@ -6386,16 +6469,16 @@
         <v>11</v>
       </c>
       <c r="B142" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="C142" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="D142">
-        <v>117.49349999999998</v>
+        <v>200.71350000000001</v>
       </c>
       <c r="E142">
-        <v>117.49349999999998</v>
+        <v>200.71350000000001</v>
       </c>
       <c r="F142">
         <v>1</v>
@@ -6415,16 +6498,16 @@
         <v>11</v>
       </c>
       <c r="B143" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C143" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D143">
-        <v>117.49349999999998</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="E143">
-        <v>117.49349999999998</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="F143">
         <v>1</v>
@@ -6441,19 +6524,19 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B144" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="C144" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="D144">
-        <v>10000</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="E144">
-        <v>10000</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="F144">
         <v>1</v>
@@ -6462,7 +6545,7 @@
         <v>10000000</v>
       </c>
       <c r="H144">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I144">
         <v>1</v>
@@ -6470,19 +6553,19 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B145" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="C145" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="D145">
-        <v>10000</v>
+        <v>421.21</v>
       </c>
       <c r="E145">
-        <v>10000</v>
+        <v>421.21</v>
       </c>
       <c r="F145">
         <v>1</v>
@@ -6491,7 +6574,7 @@
         <v>10000000</v>
       </c>
       <c r="H145">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I145">
         <v>1</v>
@@ -6499,19 +6582,19 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B146" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C146" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="D146">
-        <v>10000</v>
+        <v>14.965</v>
       </c>
       <c r="E146">
-        <v>10000</v>
+        <v>14.965</v>
       </c>
       <c r="F146">
         <v>1</v>
@@ -6520,7 +6603,7 @@
         <v>10000000</v>
       </c>
       <c r="H146">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I146">
         <v>1</v>
@@ -6528,19 +6611,19 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B147" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="C147" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D147">
-        <v>10000</v>
+        <v>117.49349999999998</v>
       </c>
       <c r="E147">
-        <v>10000</v>
+        <v>117.49349999999998</v>
       </c>
       <c r="F147">
         <v>1</v>
@@ -6549,7 +6632,7 @@
         <v>10000000</v>
       </c>
       <c r="H147">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I147">
         <v>1</v>
@@ -6557,19 +6640,19 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B148" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C148" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D148">
-        <v>10000</v>
+        <v>117.49349999999998</v>
       </c>
       <c r="E148">
-        <v>10000</v>
+        <v>117.49349999999998</v>
       </c>
       <c r="F148">
         <v>1</v>
@@ -6578,7 +6661,7 @@
         <v>10000000</v>
       </c>
       <c r="H148">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I148">
         <v>1</v>
@@ -6589,10 +6672,10 @@
         <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C149" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D149">
         <v>10000</v>
@@ -6618,10 +6701,10 @@
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C150" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D150">
         <v>10000</v>
@@ -6647,10 +6730,10 @@
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C151" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D151">
         <v>10000</v>
@@ -6676,10 +6759,10 @@
         <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C152" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D152">
         <v>10000</v>
@@ -6705,10 +6788,10 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C153" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D153">
         <v>10000</v>
@@ -6734,10 +6817,10 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C154" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D154">
         <v>10000</v>
@@ -6763,10 +6846,10 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C155" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D155">
         <v>10000</v>
@@ -6792,10 +6875,10 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C156" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="D156">
         <v>10000</v>
@@ -6821,10 +6904,10 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C157" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D157">
         <v>10000</v>
@@ -6850,10 +6933,10 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C158" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D158">
         <v>10000</v>
@@ -6879,10 +6962,10 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C159" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D159">
         <v>10000</v>
@@ -6908,10 +6991,10 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C160" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D160">
         <v>10000</v>
@@ -6937,10 +7020,10 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C161" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="D161">
         <v>10000</v>
@@ -6966,10 +7049,10 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="C162" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="D162">
         <v>10000</v>
@@ -6995,10 +7078,10 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="C163" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D163">
         <v>10000</v>
@@ -7024,10 +7107,10 @@
         <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C164" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D164">
         <v>10000</v>
@@ -7053,10 +7136,10 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="C165" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="D165">
         <v>10000</v>
@@ -7082,10 +7165,10 @@
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="C166" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="D166">
         <v>10000</v>
@@ -7111,10 +7194,10 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C167" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D167">
         <v>10000</v>
@@ -7140,10 +7223,10 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="C168" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="D168">
         <v>10000</v>
@@ -7169,10 +7252,10 @@
         <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C169" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D169">
         <v>10000</v>
@@ -7198,10 +7281,10 @@
         <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C170" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D170">
         <v>10000</v>
@@ -7227,10 +7310,10 @@
         <v>12</v>
       </c>
       <c r="B171" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C171" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D171">
         <v>10000</v>
@@ -7256,10 +7339,10 @@
         <v>12</v>
       </c>
       <c r="B172" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="C172" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D172">
         <v>10000</v>
@@ -7285,10 +7368,10 @@
         <v>12</v>
       </c>
       <c r="B173" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C173" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D173">
         <v>10000</v>
@@ -7314,10 +7397,10 @@
         <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="C174" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="D174">
         <v>10000</v>
@@ -7343,10 +7426,10 @@
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C175" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="D175">
         <v>10000</v>
@@ -7372,10 +7455,10 @@
         <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C176" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D176">
         <v>10000</v>
@@ -7401,10 +7484,10 @@
         <v>12</v>
       </c>
       <c r="B177" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C177" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D177">
         <v>10000</v>
@@ -7430,10 +7513,10 @@
         <v>12</v>
       </c>
       <c r="B178" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C178" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="D178">
         <v>10000</v>
@@ -7459,10 +7542,10 @@
         <v>12</v>
       </c>
       <c r="B179" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C179" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D179">
         <v>10000</v>
@@ -7488,10 +7571,10 @@
         <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C180" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D180">
         <v>10000</v>
@@ -7517,10 +7600,10 @@
         <v>12</v>
       </c>
       <c r="B181" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C181" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D181">
         <v>10000</v>
@@ -7546,10 +7629,10 @@
         <v>12</v>
       </c>
       <c r="B182" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C182" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D182">
         <v>10000</v>
@@ -7575,10 +7658,10 @@
         <v>12</v>
       </c>
       <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="s">
         <v>42</v>
-      </c>
-      <c r="C183" t="s">
-        <v>30</v>
       </c>
       <c r="D183">
         <v>10000</v>
@@ -7604,10 +7687,10 @@
         <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C184" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="D184">
         <v>10000</v>
@@ -7633,10 +7716,10 @@
         <v>12</v>
       </c>
       <c r="B185" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C185" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="D185">
         <v>10000</v>
@@ -7662,7 +7745,7 @@
         <v>12</v>
       </c>
       <c r="B186" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="C186" t="s">
         <v>42</v>
@@ -7691,10 +7774,10 @@
         <v>12</v>
       </c>
       <c r="B187" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C187" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D187">
         <v>10000</v>
@@ -7720,10 +7803,10 @@
         <v>12</v>
       </c>
       <c r="B188" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C188" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="D188">
         <v>10000</v>
@@ -7749,10 +7832,10 @@
         <v>12</v>
       </c>
       <c r="B189" t="s">
+        <v>42</v>
+      </c>
+      <c r="C189" t="s">
         <v>60</v>
-      </c>
-      <c r="C189" t="s">
-        <v>65</v>
       </c>
       <c r="D189">
         <v>10000</v>
@@ -7778,10 +7861,10 @@
         <v>12</v>
       </c>
       <c r="B190" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C190" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D190">
         <v>10000</v>
@@ -7807,10 +7890,10 @@
         <v>12</v>
       </c>
       <c r="B191" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C191" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="D191">
         <v>10000</v>
@@ -7836,10 +7919,10 @@
         <v>12</v>
       </c>
       <c r="B192" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C192" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="D192">
         <v>10000</v>
@@ -7865,10 +7948,10 @@
         <v>12</v>
       </c>
       <c r="B193" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C193" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="D193">
         <v>10000</v>
@@ -7894,10 +7977,10 @@
         <v>12</v>
       </c>
       <c r="B194" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C194" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D194">
         <v>10000</v>
@@ -7923,10 +8006,10 @@
         <v>12</v>
       </c>
       <c r="B195" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C195" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="D195">
         <v>10000</v>
@@ -7952,10 +8035,10 @@
         <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C196" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D196">
         <v>10000</v>
@@ -7981,7 +8064,7 @@
         <v>12</v>
       </c>
       <c r="B197" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C197" t="s">
         <v>22</v>
@@ -8010,10 +8093,10 @@
         <v>12</v>
       </c>
       <c r="B198" t="s">
+        <v>60</v>
+      </c>
+      <c r="C198" t="s">
         <v>64</v>
-      </c>
-      <c r="C198" t="s">
-        <v>24</v>
       </c>
       <c r="D198">
         <v>10000</v>
@@ -8039,10 +8122,10 @@
         <v>12</v>
       </c>
       <c r="B199" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="C199" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D199">
         <v>10000</v>
@@ -8068,7 +8151,7 @@
         <v>12</v>
       </c>
       <c r="B200" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="C200" t="s">
         <v>66</v>
@@ -8097,10 +8180,10 @@
         <v>12</v>
       </c>
       <c r="B201" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C201" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D201">
         <v>10000</v>
@@ -8126,7 +8209,7 @@
         <v>12</v>
       </c>
       <c r="B202" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C202" t="s">
         <v>61</v>
@@ -8155,10 +8238,10 @@
         <v>12</v>
       </c>
       <c r="B203" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C203" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="D203">
         <v>10000</v>
@@ -8184,7 +8267,7 @@
         <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C204" t="s">
         <v>42</v>
@@ -8213,10 +8296,10 @@
         <v>12</v>
       </c>
       <c r="B205" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C205" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D205">
         <v>10000</v>
@@ -8242,10 +8325,10 @@
         <v>12</v>
       </c>
       <c r="B206" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C206" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D206">
         <v>10000</v>
@@ -8271,10 +8354,10 @@
         <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C207" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D207">
         <v>10000</v>
@@ -8300,10 +8383,10 @@
         <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C208" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="D208">
         <v>10000</v>
@@ -8329,10 +8412,10 @@
         <v>12</v>
       </c>
       <c r="B209" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C209" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D209">
         <v>10000</v>
@@ -8358,10 +8441,10 @@
         <v>12</v>
       </c>
       <c r="B210" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C210" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D210">
         <v>10000</v>
@@ -8387,10 +8470,10 @@
         <v>12</v>
       </c>
       <c r="B211" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="C211" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="D211">
         <v>10000</v>
@@ -8416,10 +8499,10 @@
         <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="C212" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D212">
         <v>10000</v>
@@ -8445,10 +8528,10 @@
         <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="C213" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D213">
         <v>10000</v>
@@ -8474,10 +8557,10 @@
         <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="C214" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="D214">
         <v>10000</v>
@@ -8503,10 +8586,10 @@
         <v>12</v>
       </c>
       <c r="B215" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="C215" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="D215">
         <v>10000</v>
@@ -8532,10 +8615,10 @@
         <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C216" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D216">
         <v>10000</v>
@@ -8561,10 +8644,10 @@
         <v>12</v>
       </c>
       <c r="B217" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C217" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="D217">
         <v>10000</v>
@@ -8590,10 +8673,10 @@
         <v>12</v>
       </c>
       <c r="B218" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C218" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D218">
         <v>10000</v>
@@ -8619,10 +8702,10 @@
         <v>12</v>
       </c>
       <c r="B219" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C219" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D219">
         <v>10000</v>
@@ -8648,10 +8731,10 @@
         <v>12</v>
       </c>
       <c r="B220" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C220" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="D220">
         <v>10000</v>
@@ -8677,10 +8760,10 @@
         <v>12</v>
       </c>
       <c r="B221" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C221" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D221">
         <v>10000</v>
@@ -8706,10 +8789,10 @@
         <v>12</v>
       </c>
       <c r="B222" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C222" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="D222">
         <v>10000</v>
@@ -8735,10 +8818,10 @@
         <v>12</v>
       </c>
       <c r="B223" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C223" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D223">
         <v>10000</v>
@@ -8764,10 +8847,10 @@
         <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="C224" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D224">
         <v>10000</v>
@@ -8793,10 +8876,10 @@
         <v>12</v>
       </c>
       <c r="B225" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C225" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D225">
         <v>10000</v>
@@ -8822,10 +8905,10 @@
         <v>12</v>
       </c>
       <c r="B226" t="s">
+        <v>66</v>
+      </c>
+      <c r="C226" t="s">
         <v>51</v>
-      </c>
-      <c r="C226" t="s">
-        <v>68</v>
       </c>
       <c r="D226">
         <v>10000</v>
@@ -8851,10 +8934,10 @@
         <v>12</v>
       </c>
       <c r="B227" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C227" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D227">
         <v>10000</v>
@@ -8880,10 +8963,10 @@
         <v>12</v>
       </c>
       <c r="B228" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C228" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D228">
         <v>10000</v>
@@ -8909,10 +8992,10 @@
         <v>12</v>
       </c>
       <c r="B229" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="C229" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D229">
         <v>10000</v>
@@ -8938,10 +9021,10 @@
         <v>12</v>
       </c>
       <c r="B230" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="C230" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="D230">
         <v>10000</v>
@@ -8967,10 +9050,10 @@
         <v>12</v>
       </c>
       <c r="B231" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C231" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="D231">
         <v>10000</v>
@@ -8996,10 +9079,10 @@
         <v>12</v>
       </c>
       <c r="B232" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C232" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="D232">
         <v>10000</v>
@@ -9025,10 +9108,10 @@
         <v>12</v>
       </c>
       <c r="B233" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="C233" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D233">
         <v>10000</v>
@@ -9054,10 +9137,10 @@
         <v>12</v>
       </c>
       <c r="B234" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C234" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D234">
         <v>10000</v>
@@ -9083,10 +9166,10 @@
         <v>12</v>
       </c>
       <c r="B235" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="C235" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D235">
         <v>10000</v>
@@ -9112,10 +9195,10 @@
         <v>12</v>
       </c>
       <c r="B236" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C236" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="D236">
         <v>10000</v>
@@ -9141,10 +9224,10 @@
         <v>12</v>
       </c>
       <c r="B237" t="s">
+        <v>51</v>
+      </c>
+      <c r="C237" t="s">
         <v>58</v>
-      </c>
-      <c r="C237" t="s">
-        <v>65</v>
       </c>
       <c r="D237">
         <v>10000</v>
@@ -9170,10 +9253,10 @@
         <v>12</v>
       </c>
       <c r="B238" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C238" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D238">
         <v>10000</v>
@@ -9199,10 +9282,10 @@
         <v>12</v>
       </c>
       <c r="B239" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="C239" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="D239">
         <v>10000</v>
@@ -9228,10 +9311,10 @@
         <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="C240" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D240">
         <v>10000</v>
@@ -9257,10 +9340,10 @@
         <v>12</v>
       </c>
       <c r="B241" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="C241" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D241">
         <v>10000</v>
@@ -9286,10 +9369,10 @@
         <v>12</v>
       </c>
       <c r="B242" t="s">
+        <v>72</v>
+      </c>
+      <c r="C242" t="s">
         <v>53</v>
-      </c>
-      <c r="C242" t="s">
-        <v>72</v>
       </c>
       <c r="D242">
         <v>10000</v>
@@ -9315,10 +9398,10 @@
         <v>12</v>
       </c>
       <c r="B243" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="C243" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="D243">
         <v>10000</v>
@@ -9344,10 +9427,10 @@
         <v>12</v>
       </c>
       <c r="B244" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="C244" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D244">
         <v>10000</v>
@@ -9373,10 +9456,10 @@
         <v>12</v>
       </c>
       <c r="B245" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C245" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="D245">
         <v>10000</v>
@@ -9402,10 +9485,10 @@
         <v>12</v>
       </c>
       <c r="B246" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C246" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D246">
         <v>10000</v>
@@ -9431,10 +9514,10 @@
         <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="C247" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="D247">
         <v>10000</v>
@@ -9460,10 +9543,10 @@
         <v>12</v>
       </c>
       <c r="B248" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C248" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="D248">
         <v>10000</v>
@@ -9489,10 +9572,10 @@
         <v>12</v>
       </c>
       <c r="B249" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C249" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="D249">
         <v>10000</v>
@@ -9518,10 +9601,10 @@
         <v>12</v>
       </c>
       <c r="B250" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C250" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D250">
         <v>10000</v>
@@ -9547,10 +9630,10 @@
         <v>12</v>
       </c>
       <c r="B251" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="C251" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D251">
         <v>10000</v>
@@ -9579,7 +9662,7 @@
         <v>53</v>
       </c>
       <c r="C252" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="D252">
         <v>10000</v>
@@ -9605,10 +9688,10 @@
         <v>12</v>
       </c>
       <c r="B253" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C253" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="D253">
         <v>10000</v>
@@ -9634,10 +9717,10 @@
         <v>12</v>
       </c>
       <c r="B254" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C254" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D254">
         <v>10000</v>
@@ -9663,10 +9746,10 @@
         <v>12</v>
       </c>
       <c r="B255" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="C255" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="D255">
         <v>10000</v>
@@ -9692,10 +9775,10 @@
         <v>12</v>
       </c>
       <c r="B256" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C256" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D256">
         <v>10000</v>
@@ -9721,10 +9804,10 @@
         <v>12</v>
       </c>
       <c r="B257" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C257" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D257">
         <v>10000</v>
@@ -9750,10 +9833,10 @@
         <v>12</v>
       </c>
       <c r="B258" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C258" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D258">
         <v>10000</v>
@@ -9779,10 +9862,10 @@
         <v>12</v>
       </c>
       <c r="B259" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C259" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D259">
         <v>10000</v>
@@ -9808,10 +9891,10 @@
         <v>12</v>
       </c>
       <c r="B260" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="C260" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D260">
         <v>10000</v>
@@ -9837,10 +9920,10 @@
         <v>12</v>
       </c>
       <c r="B261" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="C261" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D261">
         <v>10000</v>
@@ -9866,10 +9949,10 @@
         <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="C262" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="D262">
         <v>10000</v>
@@ -9895,10 +9978,10 @@
         <v>12</v>
       </c>
       <c r="B263" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C263" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="D263">
         <v>10000</v>
@@ -9924,10 +10007,10 @@
         <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C264" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D264">
         <v>10000</v>
@@ -9953,10 +10036,10 @@
         <v>12</v>
       </c>
       <c r="B265" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="C265" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="D265">
         <v>10000</v>
@@ -9982,10 +10065,10 @@
         <v>12</v>
       </c>
       <c r="B266" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="C266" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="D266">
         <v>10000</v>
@@ -9994,7 +10077,7 @@
         <v>10000</v>
       </c>
       <c r="F266">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G266">
         <v>10000000</v>
@@ -10011,10 +10094,10 @@
         <v>12</v>
       </c>
       <c r="B267" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="C267" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="D267">
         <v>10000</v>
@@ -10023,7 +10106,7 @@
         <v>10000</v>
       </c>
       <c r="F267">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G267">
         <v>10000000</v>
@@ -10040,10 +10123,10 @@
         <v>12</v>
       </c>
       <c r="B268" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C268" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D268">
         <v>10000</v>
@@ -10052,7 +10135,7 @@
         <v>10000</v>
       </c>
       <c r="F268">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G268">
         <v>10000000</v>
@@ -10069,10 +10152,10 @@
         <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C269" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D269">
         <v>10000</v>
@@ -10081,7 +10164,7 @@
         <v>10000</v>
       </c>
       <c r="F269">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G269">
         <v>10000000</v>
@@ -10098,10 +10181,10 @@
         <v>12</v>
       </c>
       <c r="B270" t="s">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="C270" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="D270">
         <v>10000</v>
@@ -10110,7 +10193,7 @@
         <v>10000</v>
       </c>
       <c r="F270">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G270">
         <v>10000000</v>
@@ -10127,10 +10210,10 @@
         <v>12</v>
       </c>
       <c r="B271" t="s">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="C271" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D271">
         <v>10000</v>
@@ -10139,7 +10222,7 @@
         <v>10000</v>
       </c>
       <c r="F271">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G271">
         <v>10000000</v>
@@ -10156,10 +10239,10 @@
         <v>12</v>
       </c>
       <c r="B272" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="C272" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D272">
         <v>10000</v>
@@ -10168,7 +10251,7 @@
         <v>10000</v>
       </c>
       <c r="F272">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G272">
         <v>10000000</v>
@@ -10185,10 +10268,10 @@
         <v>12</v>
       </c>
       <c r="B273" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C273" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="D273">
         <v>10000</v>
@@ -10197,7 +10280,7 @@
         <v>10000</v>
       </c>
       <c r="F273">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G273">
         <v>10000000</v>
@@ -10214,10 +10297,10 @@
         <v>12</v>
       </c>
       <c r="B274" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C274" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="D274">
         <v>10000</v>
@@ -10226,7 +10309,7 @@
         <v>10000</v>
       </c>
       <c r="F274">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G274">
         <v>10000000</v>
@@ -10243,10 +10326,10 @@
         <v>12</v>
       </c>
       <c r="B275" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="C275" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D275">
         <v>10000</v>
@@ -10255,7 +10338,7 @@
         <v>10000</v>
       </c>
       <c r="F275">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G275">
         <v>10000000</v>
@@ -10272,10 +10355,10 @@
         <v>12</v>
       </c>
       <c r="B276" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C276" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D276">
         <v>10000</v>
@@ -10301,10 +10384,10 @@
         <v>12</v>
       </c>
       <c r="B277" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C277" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D277">
         <v>10000</v>
@@ -10330,10 +10413,10 @@
         <v>12</v>
       </c>
       <c r="B278" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C278" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D278">
         <v>10000</v>
@@ -10359,10 +10442,10 @@
         <v>12</v>
       </c>
       <c r="B279" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C279" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="D279">
         <v>10000</v>
@@ -10388,10 +10471,10 @@
         <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C280" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="D280">
         <v>10000</v>
@@ -10417,10 +10500,10 @@
         <v>12</v>
       </c>
       <c r="B281" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C281" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D281">
         <v>10000</v>
@@ -10446,10 +10529,10 @@
         <v>12</v>
       </c>
       <c r="B282" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="C282" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D282">
         <v>10000</v>
@@ -10475,10 +10558,10 @@
         <v>12</v>
       </c>
       <c r="B283" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C283" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D283">
         <v>10000</v>
@@ -10504,10 +10587,10 @@
         <v>12</v>
       </c>
       <c r="B284" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="C284" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D284">
         <v>10000</v>
@@ -10533,10 +10616,10 @@
         <v>12</v>
       </c>
       <c r="B285" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="C285" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D285">
         <v>10000</v>
@@ -10554,6 +10637,296 @@
         <v>1000</v>
       </c>
       <c r="I285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>12</v>
+      </c>
+      <c r="B286" t="s">
+        <v>91</v>
+      </c>
+      <c r="C286" t="s">
+        <v>59</v>
+      </c>
+      <c r="D286">
+        <v>10000</v>
+      </c>
+      <c r="E286">
+        <v>10000</v>
+      </c>
+      <c r="F286">
+        <v>100</v>
+      </c>
+      <c r="G286">
+        <v>10000000</v>
+      </c>
+      <c r="H286">
+        <v>1000</v>
+      </c>
+      <c r="I286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>12</v>
+      </c>
+      <c r="B287" t="s">
+        <v>92</v>
+      </c>
+      <c r="C287" t="s">
+        <v>67</v>
+      </c>
+      <c r="D287">
+        <v>10000</v>
+      </c>
+      <c r="E287">
+        <v>10000</v>
+      </c>
+      <c r="F287">
+        <v>100</v>
+      </c>
+      <c r="G287">
+        <v>10000000</v>
+      </c>
+      <c r="H287">
+        <v>1000</v>
+      </c>
+      <c r="I287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>12</v>
+      </c>
+      <c r="B288" t="s">
+        <v>93</v>
+      </c>
+      <c r="C288" t="s">
+        <v>65</v>
+      </c>
+      <c r="D288">
+        <v>10000</v>
+      </c>
+      <c r="E288">
+        <v>10000</v>
+      </c>
+      <c r="F288">
+        <v>100</v>
+      </c>
+      <c r="G288">
+        <v>10000000</v>
+      </c>
+      <c r="H288">
+        <v>1000</v>
+      </c>
+      <c r="I288">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>12</v>
+      </c>
+      <c r="B289" t="s">
+        <v>94</v>
+      </c>
+      <c r="C289" t="s">
+        <v>64</v>
+      </c>
+      <c r="D289">
+        <v>10000</v>
+      </c>
+      <c r="E289">
+        <v>10000</v>
+      </c>
+      <c r="F289">
+        <v>100</v>
+      </c>
+      <c r="G289">
+        <v>10000000</v>
+      </c>
+      <c r="H289">
+        <v>1000</v>
+      </c>
+      <c r="I289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>12</v>
+      </c>
+      <c r="B290" t="s">
+        <v>95</v>
+      </c>
+      <c r="C290" t="s">
+        <v>36</v>
+      </c>
+      <c r="D290">
+        <v>10000</v>
+      </c>
+      <c r="E290">
+        <v>10000</v>
+      </c>
+      <c r="F290">
+        <v>100</v>
+      </c>
+      <c r="G290">
+        <v>10000000</v>
+      </c>
+      <c r="H290">
+        <v>1000</v>
+      </c>
+      <c r="I290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>12</v>
+      </c>
+      <c r="B291" t="s">
+        <v>96</v>
+      </c>
+      <c r="C291" t="s">
+        <v>34</v>
+      </c>
+      <c r="D291">
+        <v>10000</v>
+      </c>
+      <c r="E291">
+        <v>10000</v>
+      </c>
+      <c r="F291">
+        <v>100</v>
+      </c>
+      <c r="G291">
+        <v>10000000</v>
+      </c>
+      <c r="H291">
+        <v>1000</v>
+      </c>
+      <c r="I291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>12</v>
+      </c>
+      <c r="B292" t="s">
+        <v>53</v>
+      </c>
+      <c r="C292" t="s">
+        <v>75</v>
+      </c>
+      <c r="D292">
+        <v>10000</v>
+      </c>
+      <c r="E292">
+        <v>10000</v>
+      </c>
+      <c r="F292">
+        <v>100</v>
+      </c>
+      <c r="G292">
+        <v>10000000</v>
+      </c>
+      <c r="H292">
+        <v>1000</v>
+      </c>
+      <c r="I292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>12</v>
+      </c>
+      <c r="B293" t="s">
+        <v>75</v>
+      </c>
+      <c r="C293" t="s">
+        <v>30</v>
+      </c>
+      <c r="D293">
+        <v>10000</v>
+      </c>
+      <c r="E293">
+        <v>10000</v>
+      </c>
+      <c r="F293">
+        <v>100</v>
+      </c>
+      <c r="G293">
+        <v>10000000</v>
+      </c>
+      <c r="H293">
+        <v>1000</v>
+      </c>
+      <c r="I293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>12</v>
+      </c>
+      <c r="B294" t="s">
+        <v>48</v>
+      </c>
+      <c r="C294" t="s">
+        <v>40</v>
+      </c>
+      <c r="D294">
+        <v>10000</v>
+      </c>
+      <c r="E294">
+        <v>10000</v>
+      </c>
+      <c r="F294">
+        <v>100</v>
+      </c>
+      <c r="G294">
+        <v>10000000</v>
+      </c>
+      <c r="H294">
+        <v>1000</v>
+      </c>
+      <c r="I294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>12</v>
+      </c>
+      <c r="B295" t="s">
+        <v>40</v>
+      </c>
+      <c r="C295" t="s">
+        <v>30</v>
+      </c>
+      <c r="D295">
+        <v>10000</v>
+      </c>
+      <c r="E295">
+        <v>10000</v>
+      </c>
+      <c r="F295">
+        <v>100</v>
+      </c>
+      <c r="G295">
+        <v>10000000</v>
+      </c>
+      <c r="H295">
+        <v>1000</v>
+      </c>
+      <c r="I295">
         <v>1</v>
       </c>
     </row>
@@ -10565,7 +10938,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68B577B-1347-43AB-A697-F4519763B965}">
-  <dimension ref="A1:C168"/>
+  <dimension ref="A1:C178"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -10716,10 +11089,10 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>24.425000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -10727,10 +11100,10 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C15">
-        <v>0.55586415</v>
+        <v>48.849999999999994</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -10738,10 +11111,10 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C16">
-        <v>796.255</v>
+        <v>304.82399999999996</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -10749,10 +11122,10 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="C17">
-        <v>7.5617455199999997</v>
+        <v>25.402000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -10760,10 +11133,10 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="C18">
-        <v>5.7643000000000007E-2</v>
+        <v>14.654999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
@@ -10771,10 +11144,10 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C19">
-        <v>0.53100926999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -10782,10 +11155,10 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C20">
-        <v>8.6795214499999993</v>
+        <v>0.55586415</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -10793,10 +11166,10 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C21">
-        <v>1.9156527500000002</v>
+        <v>796.255</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -10804,10 +11177,10 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C22">
-        <v>0.16949973000000002</v>
+        <v>7.5617455199999997</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -10815,10 +11188,10 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C23">
-        <v>6.3309600000000021E-2</v>
+        <v>5.7643000000000007E-2</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -10826,10 +11199,10 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C24">
-        <v>16.46245</v>
+        <v>0.53100926999999998</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -10837,10 +11210,10 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C25">
-        <v>19.829690269999997</v>
+        <v>8.6795214499999993</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -10848,10 +11221,10 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C26">
-        <v>3.9959299999999995</v>
+        <v>1.9156527500000002</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -10859,10 +11232,10 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C27">
-        <v>0.6516687699999999</v>
+        <v>0.16949973000000002</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
@@ -10870,10 +11243,10 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C28">
-        <v>5.2113180000000002E-2</v>
+        <v>6.3309600000000021E-2</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
@@ -10881,10 +11254,10 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C29">
-        <v>4.2744726999999996</v>
+        <v>16.46245</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -10892,10 +11265,10 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C30">
-        <v>0.44941999999999999</v>
+        <v>19.829690269999997</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
@@ -10903,10 +11276,10 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="C31">
-        <v>13.947075569999997</v>
+        <v>3.9959299999999995</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
@@ -10914,10 +11287,10 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C32">
-        <v>47.618979999999993</v>
+        <v>0.6516687699999999</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
@@ -10925,10 +11298,10 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="C33">
-        <v>38.415639999999996</v>
+        <v>5.2113180000000002E-2</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
@@ -10936,10 +11309,10 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="C34">
-        <v>129.941</v>
+        <v>4.2744726999999996</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
@@ -10947,10 +11320,10 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="C35">
-        <v>234.14902171</v>
+        <v>0.44941999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
@@ -10958,10 +11331,10 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C36">
-        <v>1135.3337630899998</v>
+        <v>13.947075569999997</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
@@ -10969,10 +11342,10 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C37">
-        <v>54.642437600000001</v>
+        <v>47.618979999999993</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
@@ -10980,10 +11353,10 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C38">
-        <v>88.09608999999999</v>
+        <v>38.415639999999996</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
@@ -10991,10 +11364,10 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C39">
-        <v>6238.1449999999995</v>
+        <v>129.941</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
@@ -11002,10 +11375,10 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C40">
-        <v>18.562999999999999</v>
+        <v>234.14902171</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
@@ -11013,10 +11386,10 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C41">
-        <v>320.81311303999996</v>
+        <v>1135.3337630899998</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
@@ -11024,10 +11397,10 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C42">
-        <v>190.67131999999998</v>
+        <v>54.642437600000001</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
@@ -11035,10 +11408,10 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C43">
-        <v>-708.32499999999993</v>
+        <v>88.09608999999999</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
@@ -11046,10 +11419,10 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C44">
-        <v>-166.09</v>
+        <v>6238.1449999999995</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
@@ -11057,10 +11430,10 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C45">
-        <v>-357.58199999999999</v>
+        <v>18.562999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
@@ -11068,10 +11441,10 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C46">
-        <v>-845.10500000000002</v>
+        <v>320.81311303999996</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
@@ -11079,10 +11452,10 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C47">
-        <v>-83.045000000000002</v>
+        <v>190.67131999999998</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
@@ -11090,10 +11463,10 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C48">
-        <v>-661.42899999999997</v>
+        <v>-708.32499999999993</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
@@ -11101,10 +11474,10 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="C49">
-        <v>-31.263999999999999</v>
+        <v>-166.09</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
@@ -11112,10 +11485,10 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="C50">
-        <v>-10.498540930309094</v>
+        <v>-357.58199999999999</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
@@ -11123,10 +11496,10 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C51">
-        <v>-20.327868125092017</v>
+        <v>-845.10500000000002</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
@@ -11134,10 +11507,10 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="C52">
-        <v>-397.63900000000001</v>
+        <v>-83.045000000000002</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
@@ -11145,10 +11518,10 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C53">
-        <v>-29.166899245671924</v>
+        <v>-661.42899999999997</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
@@ -11156,10 +11529,10 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C54">
-        <v>-211.03200000000001</v>
+        <v>-31.263999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
@@ -11167,10 +11540,10 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C55">
-        <v>-83.045000000000002</v>
+        <v>-10.498540930309094</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
@@ -11178,10 +11551,10 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="C56">
-        <v>-27.339084185091842</v>
+        <v>-20.327868125092017</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
@@ -11189,10 +11562,10 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="C57">
-        <v>-99.653999999999982</v>
+        <v>-397.63900000000001</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
@@ -11200,10 +11573,10 @@
         <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="C58">
-        <v>-34.696428008002286</v>
+        <v>-29.166899245671924</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
@@ -11211,10 +11584,10 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="C59">
-        <v>-19.54</v>
+        <v>-211.03200000000001</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
@@ -11222,10 +11595,10 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C60">
-        <v>-34.820653312201756</v>
+        <v>-83.045000000000002</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
@@ -11233,10 +11606,10 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C61">
-        <v>-55.689</v>
+        <v>-27.339084185091842</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
@@ -11244,10 +11617,10 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C62">
-        <v>-110.401</v>
+        <v>-99.653999999999982</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
@@ -11255,10 +11628,10 @@
         <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="C63">
-        <v>-13.995883970311864</v>
+        <v>-34.696428008002286</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
@@ -11266,10 +11639,10 @@
         <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C64">
-        <v>-9.5558311621502252</v>
+        <v>-19.54</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
@@ -11277,10 +11650,10 @@
         <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="C65">
-        <v>-316.54799999999994</v>
+        <v>-34.820653312201756</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
@@ -11288,10 +11661,10 @@
         <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C66">
-        <v>-58.62</v>
+        <v>-55.689</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
@@ -11299,10 +11672,10 @@
         <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C67">
-        <v>-286.26099999999997</v>
+        <v>-110.401</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
@@ -11310,10 +11683,10 @@
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>26</v>
       </c>
       <c r="C68">
-        <v>-12.918429819775348</v>
+        <v>-13.995883970311864</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
@@ -11321,10 +11694,10 @@
         <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>-9.5558311621502252</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
@@ -11332,10 +11705,10 @@
         <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>-316.54799999999994</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
@@ -11343,10 +11716,10 @@
         <v>11</v>
       </c>
       <c r="B71" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C71">
-        <v>-453.32799999999997</v>
+        <v>-58.62</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
@@ -11354,10 +11727,10 @@
         <v>11</v>
       </c>
       <c r="B72" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C72">
-        <v>-42.988</v>
+        <v>-286.26099999999997</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
@@ -11365,10 +11738,10 @@
         <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>-12.918429819775348</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
@@ -11376,7 +11749,7 @@
         <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -11387,7 +11760,7 @@
         <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -11398,10 +11771,10 @@
         <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>-453.32799999999997</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
@@ -11409,10 +11782,10 @@
         <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>-42.988</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
@@ -11420,10 +11793,10 @@
         <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C78">
-        <v>-10.747</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
@@ -11431,10 +11804,10 @@
         <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C79">
-        <v>-3.1361880225518983</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
@@ -11442,10 +11815,10 @@
         <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="C80">
-        <v>-24.864095362311311</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
@@ -11453,18 +11826,18 @@
         <v>11</v>
       </c>
       <c r="B81" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C81">
-        <v>-10.40036286731274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B82" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -11472,46 +11845,46 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B83" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>-10.747</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B84" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>-3.1361880225518983</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B85" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>-24.864095362311311</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B86" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>-10.40036286731274</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
@@ -11519,7 +11892,7 @@
         <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -11530,7 +11903,7 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -11541,7 +11914,7 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -11552,7 +11925,7 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -11563,7 +11936,7 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -11574,7 +11947,7 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -11585,7 +11958,7 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -11596,7 +11969,7 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -11607,7 +11980,7 @@
         <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -11618,7 +11991,7 @@
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -11629,7 +12002,7 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -11640,7 +12013,7 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -11651,7 +12024,7 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -11662,7 +12035,7 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -11673,7 +12046,7 @@
         <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -11684,7 +12057,7 @@
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -11695,7 +12068,7 @@
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -11706,7 +12079,7 @@
         <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -11717,7 +12090,7 @@
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -11728,7 +12101,7 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -11739,7 +12112,7 @@
         <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -11750,7 +12123,7 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -11761,7 +12134,7 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -11772,7 +12145,7 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -11783,7 +12156,7 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -11794,7 +12167,7 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -11805,7 +12178,7 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -11816,7 +12189,7 @@
         <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -11827,7 +12200,7 @@
         <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -11838,7 +12211,7 @@
         <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -11849,7 +12222,7 @@
         <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -11860,7 +12233,7 @@
         <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -11871,7 +12244,7 @@
         <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -11882,7 +12255,7 @@
         <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -11893,7 +12266,7 @@
         <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -11904,7 +12277,7 @@
         <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -11915,7 +12288,7 @@
         <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -11926,7 +12299,7 @@
         <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -11937,7 +12310,7 @@
         <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -11948,7 +12321,7 @@
         <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -11959,7 +12332,7 @@
         <v>12</v>
       </c>
       <c r="B127" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -11970,7 +12343,7 @@
         <v>12</v>
       </c>
       <c r="B128" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -11981,7 +12354,7 @@
         <v>12</v>
       </c>
       <c r="B129" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -11992,7 +12365,7 @@
         <v>12</v>
       </c>
       <c r="B130" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -12003,7 +12376,7 @@
         <v>12</v>
       </c>
       <c r="B131" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -12014,7 +12387,7 @@
         <v>12</v>
       </c>
       <c r="B132" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -12025,7 +12398,7 @@
         <v>12</v>
       </c>
       <c r="B133" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -12036,7 +12409,7 @@
         <v>12</v>
       </c>
       <c r="B134" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -12047,7 +12420,7 @@
         <v>12</v>
       </c>
       <c r="B135" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -12058,7 +12431,7 @@
         <v>12</v>
       </c>
       <c r="B136" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -12069,7 +12442,7 @@
         <v>12</v>
       </c>
       <c r="B137" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -12080,7 +12453,7 @@
         <v>12</v>
       </c>
       <c r="B138" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -12091,7 +12464,7 @@
         <v>12</v>
       </c>
       <c r="B139" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -12102,7 +12475,7 @@
         <v>12</v>
       </c>
       <c r="B140" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -12113,7 +12486,7 @@
         <v>12</v>
       </c>
       <c r="B141" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -12121,13 +12494,13 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C142">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.35">
@@ -12135,7 +12508,7 @@
         <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -12146,7 +12519,7 @@
         <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -12157,7 +12530,7 @@
         <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -12168,7 +12541,7 @@
         <v>12</v>
       </c>
       <c r="B146" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -12179,7 +12552,7 @@
         <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -12190,7 +12563,7 @@
         <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -12201,7 +12574,7 @@
         <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -12212,7 +12585,7 @@
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -12223,7 +12596,7 @@
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -12231,13 +12604,13 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B152" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
@@ -12245,7 +12618,7 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -12256,7 +12629,7 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -12267,7 +12640,7 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -12278,7 +12651,7 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -12289,7 +12662,7 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -12300,7 +12673,7 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -12311,7 +12684,7 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -12322,7 +12695,7 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -12333,7 +12706,7 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -12341,10 +12714,10 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -12355,7 +12728,7 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -12363,10 +12736,10 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -12377,7 +12750,7 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -12388,7 +12761,7 @@
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -12399,7 +12772,7 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -12410,9 +12783,119 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
+        <v>93</v>
+      </c>
+      <c r="C168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>12</v>
+      </c>
+      <c r="B169" t="s">
+        <v>94</v>
+      </c>
+      <c r="C169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>12</v>
+      </c>
+      <c r="B170" t="s">
+        <v>95</v>
+      </c>
+      <c r="C170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>12</v>
+      </c>
+      <c r="B171" t="s">
+        <v>96</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>11</v>
+      </c>
+      <c r="B172" t="s">
+        <v>82</v>
+      </c>
+      <c r="C172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>12</v>
+      </c>
+      <c r="B173" t="s">
+        <v>82</v>
+      </c>
+      <c r="C173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>11</v>
+      </c>
+      <c r="B174" t="s">
+        <v>75</v>
+      </c>
+      <c r="C174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>12</v>
+      </c>
+      <c r="B175" t="s">
+        <v>75</v>
+      </c>
+      <c r="C175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>12</v>
+      </c>
+      <c r="B176" t="s">
+        <v>63</v>
+      </c>
+      <c r="C176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>12</v>
+      </c>
+      <c r="B177" t="s">
+        <v>59</v>
+      </c>
+      <c r="C177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>12</v>
+      </c>
+      <c r="B178" t="s">
         <v>70</v>
       </c>
-      <c r="C168">
+      <c r="C178">
         <v>0</v>
       </c>
     </row>

--- a/01_data/01_input_data/02_processed/data_case_russia_LNG_planned.xlsx
+++ b/01_data/01_input_data/02_processed/data_case_russia_LNG_planned.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D14237B-8AD8-4905-B141-CA183AE1CB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6C024B-D51C-4A32-ACAF-F816182D1262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="103">
   <si>
     <t>Commodities</t>
   </si>
@@ -706,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0CB446-BDDD-415D-AF22-2CEB1FE45CA5}">
-  <dimension ref="A1:A89"/>
+  <dimension ref="A1:A90"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -921,236 +921,241 @@
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
         <v>70</v>
       </c>
     </row>
@@ -10938,7 +10943,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68B577B-1347-43AB-A697-F4519763B965}">
-  <dimension ref="A1:C178"/>
+  <dimension ref="A1:C180"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -11584,10 +11589,10 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="C59">
-        <v>-211.03200000000001</v>
+        <v>-6.6570737613344075</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
@@ -11595,10 +11600,10 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="C60">
-        <v>-83.045000000000002</v>
+        <v>-211.03200000000001</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
@@ -11606,10 +11611,10 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C61">
-        <v>-27.339084185091842</v>
+        <v>-83.045000000000002</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
@@ -11617,10 +11622,10 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C62">
-        <v>-99.653999999999982</v>
+        <v>-27.339084185091842</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
@@ -11628,10 +11633,10 @@
         <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C63">
-        <v>-34.696428008002286</v>
+        <v>-99.653999999999982</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
@@ -11639,10 +11644,10 @@
         <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C64">
-        <v>-19.54</v>
+        <v>-34.696428008002286</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
@@ -11650,10 +11655,10 @@
         <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C65">
-        <v>-34.820653312201756</v>
+        <v>-19.54</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
@@ -11661,10 +11666,10 @@
         <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="C66">
-        <v>-55.689</v>
+        <v>-34.820653312201756</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
@@ -11672,10 +11677,10 @@
         <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C67">
-        <v>-110.401</v>
+        <v>-55.689</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
@@ -11683,10 +11688,10 @@
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C68">
-        <v>-13.995883970311864</v>
+        <v>-110.401</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
@@ -11694,10 +11699,10 @@
         <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="C69">
-        <v>-9.5558311621502252</v>
+        <v>-13.995883970311864</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
@@ -11705,10 +11710,10 @@
         <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C70">
-        <v>-316.54799999999994</v>
+        <v>-9.5558311621502252</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
@@ -11716,10 +11721,10 @@
         <v>11</v>
       </c>
       <c r="B71" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C71">
-        <v>-58.62</v>
+        <v>-316.54799999999994</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
@@ -11727,10 +11732,10 @@
         <v>11</v>
       </c>
       <c r="B72" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C72">
-        <v>-286.26099999999997</v>
+        <v>-58.62</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
@@ -11738,10 +11743,10 @@
         <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C73">
-        <v>-12.918429819775348</v>
+        <v>-286.26099999999997</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
@@ -11749,10 +11754,10 @@
         <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>-12.918429819775348</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
@@ -11760,7 +11765,7 @@
         <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -11771,10 +11776,10 @@
         <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C76">
-        <v>-453.32799999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
@@ -11782,10 +11787,10 @@
         <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C77">
-        <v>-42.988</v>
+        <v>-453.32799999999997</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
@@ -11793,10 +11798,10 @@
         <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>-42.988</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
@@ -11804,7 +11809,7 @@
         <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -11815,7 +11820,7 @@
         <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -11826,7 +11831,7 @@
         <v>11</v>
       </c>
       <c r="B81" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -11837,7 +11842,7 @@
         <v>11</v>
       </c>
       <c r="B82" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -11848,10 +11853,10 @@
         <v>11</v>
       </c>
       <c r="B83" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C83">
-        <v>-10.747</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
@@ -11859,10 +11864,10 @@
         <v>11</v>
       </c>
       <c r="B84" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C84">
-        <v>-3.1361880225518983</v>
+        <v>-10.747</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
@@ -11870,10 +11875,10 @@
         <v>11</v>
       </c>
       <c r="B85" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C85">
-        <v>-24.864095362311311</v>
+        <v>-3.1361880225518983</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
@@ -11881,21 +11886,21 @@
         <v>11</v>
       </c>
       <c r="B86" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C86">
-        <v>-10.40036286731274</v>
+        <v>-24.864095362311311</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B87" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>-10.40036286731274</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.35">
@@ -11903,7 +11908,7 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -11914,7 +11919,7 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -11925,7 +11930,7 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -11936,7 +11941,7 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -11947,7 +11952,7 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -11958,7 +11963,7 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -11969,7 +11974,7 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -11980,7 +11985,7 @@
         <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -11991,7 +11996,7 @@
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -12002,7 +12007,7 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -12013,7 +12018,7 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -12024,7 +12029,7 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -12035,7 +12040,7 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -12046,7 +12051,7 @@
         <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -12057,7 +12062,7 @@
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -12068,7 +12073,7 @@
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -12079,7 +12084,7 @@
         <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -12090,7 +12095,7 @@
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -12101,7 +12106,7 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -12112,7 +12117,7 @@
         <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -12123,7 +12128,7 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -12134,7 +12139,7 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -12145,7 +12150,7 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -12156,7 +12161,7 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -12167,7 +12172,7 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -12178,7 +12183,7 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -12189,7 +12194,7 @@
         <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -12200,7 +12205,7 @@
         <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -12211,7 +12216,7 @@
         <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -12222,7 +12227,7 @@
         <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -12233,7 +12238,7 @@
         <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -12244,7 +12249,7 @@
         <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -12255,7 +12260,7 @@
         <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -12266,7 +12271,7 @@
         <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -12277,7 +12282,7 @@
         <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -12288,7 +12293,7 @@
         <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -12299,7 +12304,7 @@
         <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -12310,7 +12315,7 @@
         <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -12321,7 +12326,7 @@
         <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -12332,7 +12337,7 @@
         <v>12</v>
       </c>
       <c r="B127" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -12343,7 +12348,7 @@
         <v>12</v>
       </c>
       <c r="B128" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -12354,7 +12359,7 @@
         <v>12</v>
       </c>
       <c r="B129" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -12365,7 +12370,7 @@
         <v>12</v>
       </c>
       <c r="B130" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -12376,7 +12381,7 @@
         <v>12</v>
       </c>
       <c r="B131" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -12387,7 +12392,7 @@
         <v>12</v>
       </c>
       <c r="B132" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -12398,7 +12403,7 @@
         <v>12</v>
       </c>
       <c r="B133" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -12409,7 +12414,7 @@
         <v>12</v>
       </c>
       <c r="B134" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -12420,7 +12425,7 @@
         <v>12</v>
       </c>
       <c r="B135" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -12431,7 +12436,7 @@
         <v>12</v>
       </c>
       <c r="B136" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -12442,7 +12447,7 @@
         <v>12</v>
       </c>
       <c r="B137" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -12453,7 +12458,7 @@
         <v>12</v>
       </c>
       <c r="B138" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -12464,7 +12469,7 @@
         <v>12</v>
       </c>
       <c r="B139" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -12475,7 +12480,7 @@
         <v>12</v>
       </c>
       <c r="B140" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -12486,7 +12491,7 @@
         <v>12</v>
       </c>
       <c r="B141" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -12497,7 +12502,7 @@
         <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -12508,7 +12513,7 @@
         <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -12519,7 +12524,7 @@
         <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -12530,7 +12535,7 @@
         <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -12541,7 +12546,7 @@
         <v>12</v>
       </c>
       <c r="B146" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -12552,7 +12557,7 @@
         <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -12563,7 +12568,7 @@
         <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -12574,7 +12579,7 @@
         <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -12585,7 +12590,7 @@
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -12596,7 +12601,7 @@
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -12604,13 +12609,13 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C152">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.35">
@@ -12618,7 +12623,7 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -12626,13 +12631,13 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B154" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.35">
@@ -12640,7 +12645,7 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -12651,7 +12656,7 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -12662,7 +12667,7 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -12673,7 +12678,7 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -12684,7 +12689,7 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -12695,7 +12700,7 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -12706,7 +12711,7 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -12717,7 +12722,7 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -12728,7 +12733,7 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -12739,7 +12744,7 @@
         <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -12750,7 +12755,7 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -12761,7 +12766,7 @@
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -12772,7 +12777,7 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -12783,7 +12788,7 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -12794,7 +12799,7 @@
         <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -12805,7 +12810,7 @@
         <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -12816,7 +12821,7 @@
         <v>12</v>
       </c>
       <c r="B171" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -12824,10 +12829,10 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B172" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -12838,7 +12843,7 @@
         <v>12</v>
       </c>
       <c r="B173" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -12849,7 +12854,7 @@
         <v>11</v>
       </c>
       <c r="B174" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -12860,7 +12865,7 @@
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -12868,10 +12873,10 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B176" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -12882,7 +12887,7 @@
         <v>12</v>
       </c>
       <c r="B177" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -12893,9 +12898,31 @@
         <v>12</v>
       </c>
       <c r="B178" t="s">
+        <v>63</v>
+      </c>
+      <c r="C178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>12</v>
+      </c>
+      <c r="B179" t="s">
+        <v>59</v>
+      </c>
+      <c r="C179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>12</v>
+      </c>
+      <c r="B180" t="s">
         <v>70</v>
       </c>
-      <c r="C178">
+      <c r="C180">
         <v>0</v>
       </c>
     </row>

--- a/01_data/01_input_data/02_processed/data_case_russia_LNG_planned.xlsx
+++ b/01_data/01_input_data/02_processed/data_case_russia_LNG_planned.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A6C024B-D51C-4A32-ACAF-F816182D1262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D29FC3D0-F4A9-4344-85AA-BB66330832A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="103">
   <si>
     <t>Commodities</t>
   </si>
@@ -1191,7 +1191,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B147"/>
+  <dimension ref="A1:B149"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2244,129 +2244,145 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="B132" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="B133" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B134" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B135" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B136" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B137" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B138" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B139" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B140" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B141" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B142" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B143" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B144" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B145" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B146" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
+        <v>94</v>
+      </c>
+      <c r="B147" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>95</v>
+      </c>
+      <c r="B148" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
         <v>96</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B149" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2377,7 +2393,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I295"/>
+  <dimension ref="A1:I299"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -6674,19 +6690,19 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B149" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="C149" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="D149">
-        <v>10000</v>
+        <v>24.424999999999997</v>
       </c>
       <c r="E149">
-        <v>10000</v>
+        <v>24.424999999999997</v>
       </c>
       <c r="F149">
         <v>1</v>
@@ -6695,7 +6711,7 @@
         <v>10000000</v>
       </c>
       <c r="H149">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I149">
         <v>1</v>
@@ -6703,19 +6719,19 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B150" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="C150" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="D150">
-        <v>10000</v>
+        <v>24.424999999999997</v>
       </c>
       <c r="E150">
-        <v>10000</v>
+        <v>24.424999999999997</v>
       </c>
       <c r="F150">
         <v>1</v>
@@ -6724,7 +6740,7 @@
         <v>10000000</v>
       </c>
       <c r="H150">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I150">
         <v>1</v>
@@ -6735,10 +6751,10 @@
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C151" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D151">
         <v>10000</v>
@@ -6764,10 +6780,10 @@
         <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C152" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D152">
         <v>10000</v>
@@ -6793,10 +6809,10 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C153" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D153">
         <v>10000</v>
@@ -6822,10 +6838,10 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C154" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D154">
         <v>10000</v>
@@ -6851,10 +6867,10 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C155" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D155">
         <v>10000</v>
@@ -6880,10 +6896,10 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C156" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D156">
         <v>10000</v>
@@ -6909,10 +6925,10 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C157" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D157">
         <v>10000</v>
@@ -6938,10 +6954,10 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C158" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D158">
         <v>10000</v>
@@ -6967,10 +6983,10 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C159" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D159">
         <v>10000</v>
@@ -6996,10 +7012,10 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C160" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D160">
         <v>10000</v>
@@ -7025,10 +7041,10 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="C161" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="D161">
         <v>10000</v>
@@ -7054,10 +7070,10 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="C162" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="D162">
         <v>10000</v>
@@ -7083,10 +7099,10 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C163" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="D163">
         <v>10000</v>
@@ -7112,10 +7128,10 @@
         <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C164" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D164">
         <v>10000</v>
@@ -7141,10 +7157,10 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C165" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="D165">
         <v>10000</v>
@@ -7170,10 +7186,10 @@
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="C166" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="D166">
         <v>10000</v>
@@ -7199,10 +7215,10 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="C167" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D167">
         <v>10000</v>
@@ -7228,10 +7244,10 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="C168" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="D168">
         <v>10000</v>
@@ -7257,10 +7273,10 @@
         <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C169" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D169">
         <v>10000</v>
@@ -7286,10 +7302,10 @@
         <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C170" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D170">
         <v>10000</v>
@@ -7315,10 +7331,10 @@
         <v>12</v>
       </c>
       <c r="B171" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C171" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D171">
         <v>10000</v>
@@ -7344,10 +7360,10 @@
         <v>12</v>
       </c>
       <c r="B172" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C172" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D172">
         <v>10000</v>
@@ -7373,10 +7389,10 @@
         <v>12</v>
       </c>
       <c r="B173" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C173" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D173">
         <v>10000</v>
@@ -7402,10 +7418,10 @@
         <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C174" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D174">
         <v>10000</v>
@@ -7431,10 +7447,10 @@
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C175" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="D175">
         <v>10000</v>
@@ -7460,10 +7476,10 @@
         <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C176" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D176">
         <v>10000</v>
@@ -7489,10 +7505,10 @@
         <v>12</v>
       </c>
       <c r="B177" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C177" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D177">
         <v>10000</v>
@@ -7518,10 +7534,10 @@
         <v>12</v>
       </c>
       <c r="B178" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C178" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D178">
         <v>10000</v>
@@ -7547,10 +7563,10 @@
         <v>12</v>
       </c>
       <c r="B179" t="s">
+        <v>56</v>
+      </c>
+      <c r="C179" t="s">
         <v>38</v>
-      </c>
-      <c r="C179" t="s">
-        <v>16</v>
       </c>
       <c r="D179">
         <v>10000</v>
@@ -7576,10 +7592,10 @@
         <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C180" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D180">
         <v>10000</v>
@@ -7605,10 +7621,10 @@
         <v>12</v>
       </c>
       <c r="B181" t="s">
+        <v>38</v>
+      </c>
+      <c r="C181" t="s">
         <v>16</v>
-      </c>
-      <c r="C181" t="s">
-        <v>38</v>
       </c>
       <c r="D181">
         <v>10000</v>
@@ -7634,10 +7650,10 @@
         <v>12</v>
       </c>
       <c r="B182" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C182" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D182">
         <v>10000</v>
@@ -7666,7 +7682,7 @@
         <v>16</v>
       </c>
       <c r="C183" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D183">
         <v>10000</v>
@@ -7695,7 +7711,7 @@
         <v>16</v>
       </c>
       <c r="C184" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D184">
         <v>10000</v>
@@ -7721,10 +7737,10 @@
         <v>12</v>
       </c>
       <c r="B185" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C185" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="D185">
         <v>10000</v>
@@ -7750,10 +7766,10 @@
         <v>12</v>
       </c>
       <c r="B186" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C186" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D186">
         <v>10000</v>
@@ -7779,7 +7795,7 @@
         <v>12</v>
       </c>
       <c r="B187" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C187" t="s">
         <v>16</v>
@@ -7808,10 +7824,10 @@
         <v>12</v>
       </c>
       <c r="B188" t="s">
+        <v>28</v>
+      </c>
+      <c r="C188" t="s">
         <v>42</v>
-      </c>
-      <c r="C188" t="s">
-        <v>28</v>
       </c>
       <c r="D188">
         <v>10000</v>
@@ -7840,7 +7856,7 @@
         <v>42</v>
       </c>
       <c r="C189" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D189">
         <v>10000</v>
@@ -7869,7 +7885,7 @@
         <v>42</v>
       </c>
       <c r="C190" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="D190">
         <v>10000</v>
@@ -7898,7 +7914,7 @@
         <v>42</v>
       </c>
       <c r="C191" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="D191">
         <v>10000</v>
@@ -7927,7 +7943,7 @@
         <v>42</v>
       </c>
       <c r="C192" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D192">
         <v>10000</v>
@@ -7956,7 +7972,7 @@
         <v>42</v>
       </c>
       <c r="C193" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D193">
         <v>10000</v>
@@ -7985,7 +8001,7 @@
         <v>42</v>
       </c>
       <c r="C194" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D194">
         <v>10000</v>
@@ -8014,7 +8030,7 @@
         <v>42</v>
       </c>
       <c r="C195" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="D195">
         <v>10000</v>
@@ -8040,10 +8056,10 @@
         <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C196" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D196">
         <v>10000</v>
@@ -8069,10 +8085,10 @@
         <v>12</v>
       </c>
       <c r="B197" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C197" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="D197">
         <v>10000</v>
@@ -8101,7 +8117,7 @@
         <v>60</v>
       </c>
       <c r="C198" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D198">
         <v>10000</v>
@@ -8130,7 +8146,7 @@
         <v>60</v>
       </c>
       <c r="C199" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="D199">
         <v>10000</v>
@@ -8159,7 +8175,7 @@
         <v>60</v>
       </c>
       <c r="C200" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D200">
         <v>10000</v>
@@ -8185,10 +8201,10 @@
         <v>12</v>
       </c>
       <c r="B201" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C201" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D201">
         <v>10000</v>
@@ -8214,10 +8230,10 @@
         <v>12</v>
       </c>
       <c r="B202" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C202" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D202">
         <v>10000</v>
@@ -8246,7 +8262,7 @@
         <v>22</v>
       </c>
       <c r="C203" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D203">
         <v>10000</v>
@@ -8272,10 +8288,10 @@
         <v>12</v>
       </c>
       <c r="B204" t="s">
+        <v>22</v>
+      </c>
+      <c r="C204" t="s">
         <v>61</v>
-      </c>
-      <c r="C204" t="s">
-        <v>42</v>
       </c>
       <c r="D204">
         <v>10000</v>
@@ -8301,10 +8317,10 @@
         <v>12</v>
       </c>
       <c r="B205" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C205" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="D205">
         <v>10000</v>
@@ -8333,7 +8349,7 @@
         <v>61</v>
       </c>
       <c r="C206" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D206">
         <v>10000</v>
@@ -8359,7 +8375,7 @@
         <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C207" t="s">
         <v>22</v>
@@ -8388,10 +8404,10 @@
         <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C208" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D208">
         <v>10000</v>
@@ -8417,10 +8433,10 @@
         <v>12</v>
       </c>
       <c r="B209" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="C209" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="D209">
         <v>10000</v>
@@ -8446,10 +8462,10 @@
         <v>12</v>
       </c>
       <c r="B210" t="s">
+        <v>64</v>
+      </c>
+      <c r="C210" t="s">
         <v>24</v>
-      </c>
-      <c r="C210" t="s">
-        <v>66</v>
       </c>
       <c r="D210">
         <v>10000</v>
@@ -8475,10 +8491,10 @@
         <v>12</v>
       </c>
       <c r="B211" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C211" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D211">
         <v>10000</v>
@@ -8504,10 +8520,10 @@
         <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C212" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D212">
         <v>10000</v>
@@ -8536,7 +8552,7 @@
         <v>18</v>
       </c>
       <c r="C213" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D213">
         <v>10000</v>
@@ -8562,10 +8578,10 @@
         <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C214" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D214">
         <v>10000</v>
@@ -8591,10 +8607,10 @@
         <v>12</v>
       </c>
       <c r="B215" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C215" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D215">
         <v>10000</v>
@@ -8620,7 +8636,7 @@
         <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C216" t="s">
         <v>42</v>
@@ -8649,10 +8665,10 @@
         <v>12</v>
       </c>
       <c r="B217" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="C217" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D217">
         <v>10000</v>
@@ -8681,7 +8697,7 @@
         <v>62</v>
       </c>
       <c r="C218" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="D218">
         <v>10000</v>
@@ -8707,10 +8723,10 @@
         <v>12</v>
       </c>
       <c r="B219" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C219" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D219">
         <v>10000</v>
@@ -8736,10 +8752,10 @@
         <v>12</v>
       </c>
       <c r="B220" t="s">
+        <v>62</v>
+      </c>
+      <c r="C220" t="s">
         <v>65</v>
-      </c>
-      <c r="C220" t="s">
-        <v>62</v>
       </c>
       <c r="D220">
         <v>10000</v>
@@ -8768,7 +8784,7 @@
         <v>65</v>
       </c>
       <c r="C221" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D221">
         <v>10000</v>
@@ -8797,7 +8813,7 @@
         <v>65</v>
       </c>
       <c r="C222" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D222">
         <v>10000</v>
@@ -8823,10 +8839,10 @@
         <v>12</v>
       </c>
       <c r="B223" t="s">
+        <v>65</v>
+      </c>
+      <c r="C223" t="s">
         <v>66</v>
-      </c>
-      <c r="C223" t="s">
-        <v>24</v>
       </c>
       <c r="D223">
         <v>10000</v>
@@ -8852,10 +8868,10 @@
         <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C224" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D224">
         <v>10000</v>
@@ -8884,7 +8900,7 @@
         <v>66</v>
       </c>
       <c r="C225" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="D225">
         <v>10000</v>
@@ -8913,7 +8929,7 @@
         <v>66</v>
       </c>
       <c r="C226" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D226">
         <v>10000</v>
@@ -8939,10 +8955,10 @@
         <v>12</v>
       </c>
       <c r="B227" t="s">
+        <v>66</v>
+      </c>
+      <c r="C227" t="s">
         <v>67</v>
-      </c>
-      <c r="C227" t="s">
-        <v>68</v>
       </c>
       <c r="D227">
         <v>10000</v>
@@ -8968,10 +8984,10 @@
         <v>12</v>
       </c>
       <c r="B228" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C228" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D228">
         <v>10000</v>
@@ -8997,10 +9013,10 @@
         <v>12</v>
       </c>
       <c r="B229" t="s">
+        <v>67</v>
+      </c>
+      <c r="C229" t="s">
         <v>68</v>
-      </c>
-      <c r="C229" t="s">
-        <v>67</v>
       </c>
       <c r="D229">
         <v>10000</v>
@@ -9026,10 +9042,10 @@
         <v>12</v>
       </c>
       <c r="B230" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C230" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="D230">
         <v>10000</v>
@@ -9058,7 +9074,7 @@
         <v>68</v>
       </c>
       <c r="C231" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D231">
         <v>10000</v>
@@ -9087,7 +9103,7 @@
         <v>68</v>
       </c>
       <c r="C232" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="D232">
         <v>10000</v>
@@ -9116,7 +9132,7 @@
         <v>68</v>
       </c>
       <c r="C233" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D233">
         <v>10000</v>
@@ -9142,10 +9158,10 @@
         <v>12</v>
       </c>
       <c r="B234" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="C234" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D234">
         <v>10000</v>
@@ -9171,10 +9187,10 @@
         <v>12</v>
       </c>
       <c r="B235" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C235" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="D235">
         <v>10000</v>
@@ -9200,7 +9216,7 @@
         <v>12</v>
       </c>
       <c r="B236" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C236" t="s">
         <v>68</v>
@@ -9232,7 +9248,7 @@
         <v>51</v>
       </c>
       <c r="C237" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D237">
         <v>10000</v>
@@ -9261,7 +9277,7 @@
         <v>51</v>
       </c>
       <c r="C238" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D238">
         <v>10000</v>
@@ -9287,10 +9303,10 @@
         <v>12</v>
       </c>
       <c r="B239" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C239" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="D239">
         <v>10000</v>
@@ -9316,10 +9332,10 @@
         <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C240" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D240">
         <v>10000</v>
@@ -9345,10 +9361,10 @@
         <v>12</v>
       </c>
       <c r="B241" t="s">
+        <v>26</v>
+      </c>
+      <c r="C241" t="s">
         <v>72</v>
-      </c>
-      <c r="C241" t="s">
-        <v>26</v>
       </c>
       <c r="D241">
         <v>10000</v>
@@ -9374,7 +9390,7 @@
         <v>12</v>
       </c>
       <c r="B242" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="C242" t="s">
         <v>53</v>
@@ -9403,10 +9419,10 @@
         <v>12</v>
       </c>
       <c r="B243" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C243" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D243">
         <v>10000</v>
@@ -9432,10 +9448,10 @@
         <v>12</v>
       </c>
       <c r="B244" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C244" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="D244">
         <v>10000</v>
@@ -9461,10 +9477,10 @@
         <v>12</v>
       </c>
       <c r="B245" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C245" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D245">
         <v>10000</v>
@@ -9490,10 +9506,10 @@
         <v>12</v>
       </c>
       <c r="B246" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C246" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D246">
         <v>10000</v>
@@ -9519,10 +9535,10 @@
         <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C247" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D247">
         <v>10000</v>
@@ -9551,7 +9567,7 @@
         <v>58</v>
       </c>
       <c r="C248" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="D248">
         <v>10000</v>
@@ -9580,7 +9596,7 @@
         <v>58</v>
       </c>
       <c r="C249" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D249">
         <v>10000</v>
@@ -9606,10 +9622,10 @@
         <v>12</v>
       </c>
       <c r="B250" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C250" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D250">
         <v>10000</v>
@@ -9635,10 +9651,10 @@
         <v>12</v>
       </c>
       <c r="B251" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C251" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D251">
         <v>10000</v>
@@ -9664,10 +9680,10 @@
         <v>12</v>
       </c>
       <c r="B252" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C252" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="D252">
         <v>10000</v>
@@ -9696,7 +9712,7 @@
         <v>53</v>
       </c>
       <c r="C253" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="D253">
         <v>10000</v>
@@ -9722,10 +9738,10 @@
         <v>12</v>
       </c>
       <c r="B254" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C254" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="D254">
         <v>10000</v>
@@ -9751,10 +9767,10 @@
         <v>12</v>
       </c>
       <c r="B255" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C255" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D255">
         <v>10000</v>
@@ -9780,10 +9796,10 @@
         <v>12</v>
       </c>
       <c r="B256" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C256" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D256">
         <v>10000</v>
@@ -9809,10 +9825,10 @@
         <v>12</v>
       </c>
       <c r="B257" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="C257" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="D257">
         <v>10000</v>
@@ -9838,10 +9854,10 @@
         <v>12</v>
       </c>
       <c r="B258" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C258" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D258">
         <v>10000</v>
@@ -9867,10 +9883,10 @@
         <v>12</v>
       </c>
       <c r="B259" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="C259" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D259">
         <v>10000</v>
@@ -9896,10 +9912,10 @@
         <v>12</v>
       </c>
       <c r="B260" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C260" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D260">
         <v>10000</v>
@@ -9925,10 +9941,10 @@
         <v>12</v>
       </c>
       <c r="B261" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C261" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D261">
         <v>10000</v>
@@ -9954,10 +9970,10 @@
         <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C262" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="D262">
         <v>10000</v>
@@ -9983,10 +9999,10 @@
         <v>12</v>
       </c>
       <c r="B263" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C263" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D263">
         <v>10000</v>
@@ -10012,10 +10028,10 @@
         <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C264" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D264">
         <v>10000</v>
@@ -10041,10 +10057,10 @@
         <v>12</v>
       </c>
       <c r="B265" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C265" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D265">
         <v>10000</v>
@@ -10070,10 +10086,10 @@
         <v>12</v>
       </c>
       <c r="B266" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="C266" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D266">
         <v>10000</v>
@@ -10099,10 +10115,10 @@
         <v>12</v>
       </c>
       <c r="B267" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="C267" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D267">
         <v>10000</v>
@@ -10131,7 +10147,7 @@
         <v>48</v>
       </c>
       <c r="C268" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="D268">
         <v>10000</v>
@@ -10160,7 +10176,7 @@
         <v>48</v>
       </c>
       <c r="C269" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D269">
         <v>10000</v>
@@ -10189,7 +10205,7 @@
         <v>48</v>
       </c>
       <c r="C270" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D270">
         <v>10000</v>
@@ -10215,10 +10231,10 @@
         <v>12</v>
       </c>
       <c r="B271" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C271" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D271">
         <v>10000</v>
@@ -10244,10 +10260,10 @@
         <v>12</v>
       </c>
       <c r="B272" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C272" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="D272">
         <v>10000</v>
@@ -10273,10 +10289,10 @@
         <v>12</v>
       </c>
       <c r="B273" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="C273" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="D273">
         <v>10000</v>
@@ -10302,10 +10318,10 @@
         <v>12</v>
       </c>
       <c r="B274" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C274" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D274">
         <v>10000</v>
@@ -10331,10 +10347,10 @@
         <v>12</v>
       </c>
       <c r="B275" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="C275" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D275">
         <v>10000</v>
@@ -10360,10 +10376,10 @@
         <v>12</v>
       </c>
       <c r="B276" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C276" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D276">
         <v>10000</v>
@@ -10372,7 +10388,7 @@
         <v>10000</v>
       </c>
       <c r="F276">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G276">
         <v>10000000</v>
@@ -10389,10 +10405,10 @@
         <v>12</v>
       </c>
       <c r="B277" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="C277" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D277">
         <v>10000</v>
@@ -10401,7 +10417,7 @@
         <v>10000</v>
       </c>
       <c r="F277">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G277">
         <v>10000000</v>
@@ -10418,10 +10434,10 @@
         <v>12</v>
       </c>
       <c r="B278" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C278" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D278">
         <v>10000</v>
@@ -10447,10 +10463,10 @@
         <v>12</v>
       </c>
       <c r="B279" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C279" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="D279">
         <v>10000</v>
@@ -10476,10 +10492,10 @@
         <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C280" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D280">
         <v>10000</v>
@@ -10505,10 +10521,10 @@
         <v>12</v>
       </c>
       <c r="B281" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C281" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D281">
         <v>10000</v>
@@ -10534,10 +10550,10 @@
         <v>12</v>
       </c>
       <c r="B282" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C282" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D282">
         <v>10000</v>
@@ -10563,10 +10579,10 @@
         <v>12</v>
       </c>
       <c r="B283" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C283" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D283">
         <v>10000</v>
@@ -10592,10 +10608,10 @@
         <v>12</v>
       </c>
       <c r="B284" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C284" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="D284">
         <v>10000</v>
@@ -10621,10 +10637,10 @@
         <v>12</v>
       </c>
       <c r="B285" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C285" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="D285">
         <v>10000</v>
@@ -10650,10 +10666,10 @@
         <v>12</v>
       </c>
       <c r="B286" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C286" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="D286">
         <v>10000</v>
@@ -10679,10 +10695,10 @@
         <v>12</v>
       </c>
       <c r="B287" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C287" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D287">
         <v>10000</v>
@@ -10708,10 +10724,10 @@
         <v>12</v>
       </c>
       <c r="B288" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C288" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D288">
         <v>10000</v>
@@ -10737,10 +10753,10 @@
         <v>12</v>
       </c>
       <c r="B289" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C289" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D289">
         <v>10000</v>
@@ -10766,10 +10782,10 @@
         <v>12</v>
       </c>
       <c r="B290" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C290" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="D290">
         <v>10000</v>
@@ -10795,10 +10811,10 @@
         <v>12</v>
       </c>
       <c r="B291" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C291" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="D291">
         <v>10000</v>
@@ -10824,10 +10840,10 @@
         <v>12</v>
       </c>
       <c r="B292" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C292" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="D292">
         <v>10000</v>
@@ -10853,10 +10869,10 @@
         <v>12</v>
       </c>
       <c r="B293" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="C293" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D293">
         <v>10000</v>
@@ -10882,10 +10898,10 @@
         <v>12</v>
       </c>
       <c r="B294" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C294" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="D294">
         <v>10000</v>
@@ -10911,7 +10927,7 @@
         <v>12</v>
       </c>
       <c r="B295" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="C295" t="s">
         <v>30</v>
@@ -10932,6 +10948,122 @@
         <v>1000</v>
       </c>
       <c r="I295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>12</v>
+      </c>
+      <c r="B296" t="s">
+        <v>48</v>
+      </c>
+      <c r="C296" t="s">
+        <v>40</v>
+      </c>
+      <c r="D296">
+        <v>10000</v>
+      </c>
+      <c r="E296">
+        <v>10000</v>
+      </c>
+      <c r="F296">
+        <v>100</v>
+      </c>
+      <c r="G296">
+        <v>10000000</v>
+      </c>
+      <c r="H296">
+        <v>1000</v>
+      </c>
+      <c r="I296">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>12</v>
+      </c>
+      <c r="B297" t="s">
+        <v>40</v>
+      </c>
+      <c r="C297" t="s">
+        <v>30</v>
+      </c>
+      <c r="D297">
+        <v>10000</v>
+      </c>
+      <c r="E297">
+        <v>10000</v>
+      </c>
+      <c r="F297">
+        <v>100</v>
+      </c>
+      <c r="G297">
+        <v>10000000</v>
+      </c>
+      <c r="H297">
+        <v>1000</v>
+      </c>
+      <c r="I297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>12</v>
+      </c>
+      <c r="B298" t="s">
+        <v>102</v>
+      </c>
+      <c r="C298" t="s">
+        <v>72</v>
+      </c>
+      <c r="D298">
+        <v>10000</v>
+      </c>
+      <c r="E298">
+        <v>10000</v>
+      </c>
+      <c r="F298">
+        <v>100</v>
+      </c>
+      <c r="G298">
+        <v>10000000</v>
+      </c>
+      <c r="H298">
+        <v>1000</v>
+      </c>
+      <c r="I298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>12</v>
+      </c>
+      <c r="B299" t="s">
+        <v>72</v>
+      </c>
+      <c r="C299" t="s">
+        <v>102</v>
+      </c>
+      <c r="D299">
+        <v>10000</v>
+      </c>
+      <c r="E299">
+        <v>10000</v>
+      </c>
+      <c r="F299">
+        <v>100</v>
+      </c>
+      <c r="G299">
+        <v>10000000</v>
+      </c>
+      <c r="H299">
+        <v>1000</v>
+      </c>
+      <c r="I299">
         <v>1</v>
       </c>
     </row>
